--- a/data/model_data/twfe_POEWC_perfirm.xlsx
+++ b/data/model_data/twfe_POEWC_perfirm.xlsx
@@ -388,16 +388,16 @@
         </is>
       </c>
       <c r="B2">
-        <v>47.00555469598082</v>
+        <v>369.0801642678051</v>
       </c>
       <c r="C2">
-        <v>20.37576189709791</v>
+        <v>79.29127285222306</v>
       </c>
       <c r="D2">
-        <v>2.306934824492416</v>
+        <v>4.654738800267062</v>
       </c>
       <c r="E2">
-        <v>0.02116650011122812</v>
+        <v>3.470357583549076E-06</v>
       </c>
     </row>
     <row r="3">
@@ -407,16 +407,16 @@
         </is>
       </c>
       <c r="B3">
-        <v>-2.971478089909075</v>
+        <v>7.256203160384517</v>
       </c>
       <c r="C3">
-        <v>5.48638174403219</v>
+        <v>21.34998406609136</v>
       </c>
       <c r="D3">
-        <v>-0.5416097946777582</v>
+        <v>0.3398692541372441</v>
       </c>
       <c r="E3">
-        <v>0.58815141873129</v>
+        <v>0.7339928968615574</v>
       </c>
     </row>
     <row r="4">
@@ -426,16 +426,16 @@
         </is>
       </c>
       <c r="B4">
-        <v>106.3770731427346</v>
+        <v>710.0085692194162</v>
       </c>
       <c r="C4">
-        <v>28.32702233870727</v>
+        <v>110.2332108459396</v>
       </c>
       <c r="D4">
-        <v>3.755321398443507</v>
+        <v>6.440967869580742</v>
       </c>
       <c r="E4">
-        <v>0.0001783773029741578</v>
+        <v>1.503107615522148E-10</v>
       </c>
     </row>
     <row r="5">
@@ -445,16 +445,16 @@
         </is>
       </c>
       <c r="B5">
-        <v>-31.14435547666286</v>
+        <v>-227.229665951836</v>
       </c>
       <c r="C5">
-        <v>28.32702233870728</v>
+        <v>110.2332108459396</v>
       </c>
       <c r="D5">
-        <v>-1.099457440470397</v>
+        <v>-2.061353962277384</v>
       </c>
       <c r="E5">
-        <v>0.2717091331944915</v>
+        <v>0.03940628381367535</v>
       </c>
     </row>
     <row r="6">
@@ -464,16 +464,16 @@
         </is>
       </c>
       <c r="B6">
-        <v>-32.54785295460682</v>
+        <v>-247.0378756253597</v>
       </c>
       <c r="C6">
-        <v>28.32702233870482</v>
+        <v>110.2332108459301</v>
       </c>
       <c r="D6">
-        <v>-1.149003681553032</v>
+        <v>-2.241047627385524</v>
       </c>
       <c r="E6">
-        <v>0.250700389976376</v>
+        <v>0.02513912019100611</v>
       </c>
     </row>
     <row r="7">
@@ -483,16 +483,16 @@
         </is>
       </c>
       <c r="B7">
-        <v>-30.28156665988984</v>
+        <v>-216.0888906512855</v>
       </c>
       <c r="C7">
-        <v>28.42524124579383</v>
+        <v>110.6154248804566</v>
       </c>
       <c r="D7">
-        <v>-1.065305528915104</v>
+        <v>-1.953514990199742</v>
       </c>
       <c r="E7">
-        <v>0.286874269846504</v>
+        <v>0.050906498685792</v>
       </c>
     </row>
     <row r="8">
@@ -502,16 +502,16 @@
         </is>
       </c>
       <c r="B8">
-        <v>6.393137981771136</v>
+        <v>-189.604554802611</v>
       </c>
       <c r="C8">
-        <v>28.42524124579</v>
+        <v>110.6154248804417</v>
       </c>
       <c r="D8">
-        <v>0.2249105971164979</v>
+        <v>-1.714087840891488</v>
       </c>
       <c r="E8">
-        <v>0.8220732289278653</v>
+        <v>0.08667716222907602</v>
       </c>
     </row>
     <row r="9">
@@ -521,16 +521,16 @@
         </is>
       </c>
       <c r="B9">
-        <v>232.5965895302573</v>
+        <v>143.747899266933</v>
       </c>
       <c r="C9">
-        <v>28.32702233870529</v>
+        <v>110.2332108459319</v>
       </c>
       <c r="D9">
-        <v>8.211120348235243</v>
+        <v>1.304034402734064</v>
       </c>
       <c r="E9">
-        <v>4.0208169660445E-16</v>
+        <v>0.192381236264945</v>
       </c>
     </row>
     <row r="10">
@@ -540,16 +540,16 @@
         </is>
       </c>
       <c r="B10">
-        <v>161.348250092164</v>
+        <v>237.0792343665766</v>
       </c>
       <c r="C10">
-        <v>28.42524124579224</v>
+        <v>110.6154248804504</v>
       </c>
       <c r="D10">
-        <v>5.676231511880246</v>
+        <v>2.14327463482425</v>
       </c>
       <c r="E10">
-        <v>1.591245058466935E-08</v>
+        <v>0.03221884580236025</v>
       </c>
     </row>
     <row r="11">
@@ -559,16 +559,16 @@
         </is>
       </c>
       <c r="B11">
-        <v>-21.75015104309385</v>
+        <v>-254.9357304753924</v>
       </c>
       <c r="C11">
-        <v>28.4252412457939</v>
+        <v>110.6154248804569</v>
       </c>
       <c r="D11">
-        <v>-0.765170323622574</v>
+        <v>-2.304703261329999</v>
       </c>
       <c r="E11">
-        <v>0.4442660171330832</v>
+        <v>0.02129151963125432</v>
       </c>
     </row>
     <row r="12">
@@ -578,16 +578,16 @@
         </is>
       </c>
       <c r="B12">
-        <v>-34.00634566703999</v>
+        <v>-272.1584634643433</v>
       </c>
       <c r="C12">
-        <v>28.42524124579298</v>
+        <v>110.6154248804533</v>
       </c>
       <c r="D12">
-        <v>-1.196343256086632</v>
+        <v>-2.46040245976975</v>
       </c>
       <c r="E12">
-        <v>0.2317132478219724</v>
+        <v>0.01396734411985355</v>
       </c>
     </row>
     <row r="13">
@@ -597,16 +597,16 @@
         </is>
       </c>
       <c r="B13">
-        <v>11.93250856117317</v>
+        <v>-197.1264227213479</v>
       </c>
       <c r="C13">
-        <v>28.42524124579404</v>
+        <v>110.6154248804574</v>
       </c>
       <c r="D13">
-        <v>0.4197856566279371</v>
+        <v>-1.782088012900401</v>
       </c>
       <c r="E13">
-        <v>0.6746899342313768</v>
+        <v>0.07489597942150629</v>
       </c>
     </row>
     <row r="14">
@@ -616,16 +616,16 @@
         </is>
       </c>
       <c r="B14">
-        <v>4.231218758133842</v>
+        <v>-217.463261078144</v>
       </c>
       <c r="C14">
-        <v>28.32046230008606</v>
+        <v>110.2076827790697</v>
       </c>
       <c r="D14">
-        <v>0.1494050031139846</v>
+        <v>-1.973213260586258</v>
       </c>
       <c r="E14">
-        <v>0.8812500636162663</v>
+        <v>0.04861730180160387</v>
       </c>
     </row>
     <row r="15">
@@ -635,16 +635,16 @@
         </is>
       </c>
       <c r="B15">
-        <v>-23.16094977221285</v>
+        <v>-292.7915006236807</v>
       </c>
       <c r="C15">
-        <v>28.42524124579471</v>
+        <v>110.61542488046</v>
       </c>
       <c r="D15">
-        <v>-0.8148022235568302</v>
+        <v>-2.646931935036139</v>
       </c>
       <c r="E15">
-        <v>0.4152885656154948</v>
+        <v>0.008190270663442217</v>
       </c>
     </row>
     <row r="16">
@@ -654,16 +654,16 @@
         </is>
       </c>
       <c r="B16">
-        <v>-16.00021230861306</v>
+        <v>-265.5220031140926</v>
       </c>
       <c r="C16">
-        <v>28.32046230008513</v>
+        <v>110.207682779066</v>
       </c>
       <c r="D16">
-        <v>-0.5649700255269124</v>
+        <v>-2.409287596096055</v>
       </c>
       <c r="E16">
-        <v>0.5721614520125045</v>
+        <v>0.01607913188937849</v>
       </c>
     </row>
     <row r="17">
@@ -673,16 +673,16 @@
         </is>
       </c>
       <c r="B17">
-        <v>50.38136217928925</v>
+        <v>-126.8740488034538</v>
       </c>
       <c r="C17">
-        <v>28.32046230008985</v>
+        <v>110.2076827790844</v>
       </c>
       <c r="D17">
-        <v>1.778973861564732</v>
+        <v>-1.151226898198901</v>
       </c>
       <c r="E17">
-        <v>0.07540532936656377</v>
+        <v>0.2497850598427648</v>
       </c>
     </row>
     <row r="18">
@@ -692,16 +692,16 @@
         </is>
       </c>
       <c r="B18">
-        <v>-30.76026724187221</v>
+        <v>-295.2965477694624</v>
       </c>
       <c r="C18">
-        <v>28.42524124579113</v>
+        <v>110.6154248804461</v>
       </c>
       <c r="D18">
-        <v>-1.082146215607821</v>
+        <v>-2.669578389167884</v>
       </c>
       <c r="E18">
-        <v>0.279326121964462</v>
+        <v>0.00765991749497132</v>
       </c>
     </row>
     <row r="19">
@@ -711,16 +711,16 @@
         </is>
       </c>
       <c r="B19">
-        <v>69.29218431287657</v>
+        <v>-120.5402888985869</v>
       </c>
       <c r="C19">
-        <v>28.32046230008811</v>
+        <v>110.2076827790776</v>
       </c>
       <c r="D19">
-        <v>2.446717980047274</v>
+        <v>-1.093755769642866</v>
       </c>
       <c r="E19">
-        <v>0.01450723058660218</v>
+        <v>0.2742020042806494</v>
       </c>
     </row>
     <row r="20">
@@ -730,16 +730,16 @@
         </is>
       </c>
       <c r="B20">
-        <v>-27.50333875719297</v>
+        <v>-261.8167917254156</v>
       </c>
       <c r="C20">
-        <v>28.32046230008657</v>
+        <v>110.2076827790716</v>
       </c>
       <c r="D20">
-        <v>-0.9711472385501594</v>
+        <v>-2.375667332106673</v>
       </c>
       <c r="E20">
-        <v>0.3315996906339338</v>
+        <v>0.01761681328490543</v>
       </c>
     </row>
     <row r="21">
@@ -749,16 +749,16 @@
         </is>
       </c>
       <c r="B21">
-        <v>-11.85189210676806</v>
+        <v>-250.0077572785802</v>
       </c>
       <c r="C21">
-        <v>28.42524124579474</v>
+        <v>110.6154248804601</v>
       </c>
       <c r="D21">
-        <v>-0.4169495697251626</v>
+        <v>-2.260152754905191</v>
       </c>
       <c r="E21">
-        <v>0.6767628220523227</v>
+        <v>0.02392556932522525</v>
       </c>
     </row>
     <row r="22">
@@ -768,16 +768,16 @@
         </is>
       </c>
       <c r="B22">
-        <v>-34.22401873214973</v>
+        <v>-313.8068933694299</v>
       </c>
       <c r="C22">
-        <v>28.32046230008708</v>
+        <v>110.2076827790736</v>
       </c>
       <c r="D22">
-        <v>-1.208455510701338</v>
+        <v>-2.847413950246089</v>
       </c>
       <c r="E22">
-        <v>0.2270238329610438</v>
+        <v>0.004455405078939149</v>
       </c>
     </row>
     <row r="23">
@@ -787,16 +787,16 @@
         </is>
       </c>
       <c r="B23">
-        <v>889.5134006440219</v>
+        <v>1933.535451032124</v>
       </c>
       <c r="C23">
-        <v>28.42524124579572</v>
+        <v>110.615424880464</v>
       </c>
       <c r="D23">
-        <v>31.29308184061891</v>
+        <v>17.47979952273012</v>
       </c>
       <c r="E23">
-        <v>1.893782979498468E-173</v>
+        <v>1.607243003394472E-63</v>
       </c>
     </row>
     <row r="24">
@@ -806,16 +806,16 @@
         </is>
       </c>
       <c r="B24">
-        <v>638.380669478342</v>
+        <v>1636.846298440491</v>
       </c>
       <c r="C24">
-        <v>28.42524124579461</v>
+        <v>110.6154248804596</v>
       </c>
       <c r="D24">
-        <v>22.4582322435975</v>
+        <v>14.79763152570634</v>
       </c>
       <c r="E24">
-        <v>3.638800464339209E-99</v>
+        <v>5.920423601082863E-47</v>
       </c>
     </row>
     <row r="25">
@@ -825,16 +825,16 @@
         </is>
       </c>
       <c r="B25">
-        <v>49.4521666754484</v>
+        <v>-231.2148192275442</v>
       </c>
       <c r="C25">
-        <v>28.42524124579214</v>
+        <v>110.61542488045</v>
       </c>
       <c r="D25">
-        <v>1.739727246211813</v>
+        <v>-2.090258383742001</v>
       </c>
       <c r="E25">
-        <v>0.08207031374152435</v>
+        <v>0.03672842323095626</v>
       </c>
     </row>
     <row r="26">
@@ -844,16 +844,16 @@
         </is>
       </c>
       <c r="B26">
-        <v>74.33330881427881</v>
+        <v>36.61597536843085</v>
       </c>
       <c r="C26">
-        <v>28.42524124579202</v>
+        <v>110.6154248804496</v>
       </c>
       <c r="D26">
-        <v>2.615045838011414</v>
+        <v>0.3310205191364993</v>
       </c>
       <c r="E26">
-        <v>0.008992753773007721</v>
+        <v>0.7406658176439138</v>
       </c>
     </row>
     <row r="27">
@@ -863,16 +863,16 @@
         </is>
       </c>
       <c r="B27">
-        <v>-25.98294925436643</v>
+        <v>-306.8802302722722</v>
       </c>
       <c r="C27">
-        <v>28.32046230008931</v>
+        <v>110.2076827790823</v>
       </c>
       <c r="D27">
-        <v>-0.9174620449004639</v>
+        <v>-2.784562950002601</v>
       </c>
       <c r="E27">
-        <v>0.3590180657475674</v>
+        <v>0.005413607536190589</v>
       </c>
     </row>
     <row r="28">
@@ -882,16 +882,16 @@
         </is>
       </c>
       <c r="B28">
-        <v>52.20095401008756</v>
+        <v>-85.09747982218371</v>
       </c>
       <c r="C28">
-        <v>28.32046230009004</v>
+        <v>110.2076827790851</v>
       </c>
       <c r="D28">
-        <v>1.843223936705355</v>
+        <v>-0.7721556036412123</v>
       </c>
       <c r="E28">
-        <v>0.06545339228584997</v>
+        <v>0.4401191703706547</v>
       </c>
     </row>
     <row r="29">
@@ -901,16 +901,16 @@
         </is>
       </c>
       <c r="B29">
-        <v>69.69689490423359</v>
+        <v>38.50366633047258</v>
       </c>
       <c r="C29">
-        <v>28.42524124579204</v>
+        <v>110.6154248804497</v>
       </c>
       <c r="D29">
-        <v>2.451936794540002</v>
+        <v>0.3480858693268716</v>
       </c>
       <c r="E29">
-        <v>0.01429920054388973</v>
+        <v>0.7278146045608924</v>
       </c>
     </row>
     <row r="30">
@@ -920,16 +920,16 @@
         </is>
       </c>
       <c r="B30">
-        <v>-26.11639091526464</v>
+        <v>-281.1585121047543</v>
       </c>
       <c r="C30">
-        <v>28.32046230008804</v>
+        <v>110.2076827790773</v>
       </c>
       <c r="D30">
-        <v>-0.9221738910379107</v>
+        <v>-2.551169800642352</v>
       </c>
       <c r="E30">
-        <v>0.3565560180882789</v>
+        <v>0.01081466205670582</v>
       </c>
     </row>
     <row r="31">
@@ -939,16 +939,16 @@
         </is>
       </c>
       <c r="B31">
-        <v>-23.881538030386</v>
+        <v>-238.6860300013306</v>
       </c>
       <c r="C31">
-        <v>28.42524124579245</v>
+        <v>110.6154248804513</v>
       </c>
       <c r="D31">
-        <v>-0.8401525188082963</v>
+        <v>-2.157800598418285</v>
       </c>
       <c r="E31">
-        <v>0.4009295374506048</v>
+        <v>0.031069436880424</v>
       </c>
     </row>
     <row r="32">
@@ -958,16 +958,16 @@
         </is>
       </c>
       <c r="B32">
-        <v>-42.42652946329237</v>
+        <v>-302.9024481249874</v>
       </c>
       <c r="C32">
-        <v>28.32702233870998</v>
+        <v>110.2332108459501</v>
       </c>
       <c r="D32">
-        <v>-1.497740530437428</v>
+        <v>-2.747832942544789</v>
       </c>
       <c r="E32">
-        <v>0.1343682821114596</v>
+        <v>0.006056254855160623</v>
       </c>
     </row>
     <row r="33">
@@ -977,16 +977,16 @@
         </is>
       </c>
       <c r="B33">
-        <v>-26.08778402680345</v>
+        <v>-284.5492986717588</v>
       </c>
       <c r="C33">
-        <v>28.32702233870366</v>
+        <v>110.2332108459256</v>
       </c>
       <c r="D33">
-        <v>-0.9209504520056561</v>
+        <v>-2.581339112669748</v>
       </c>
       <c r="E33">
-        <v>0.3571942672709407</v>
+        <v>0.009916783048003778</v>
       </c>
     </row>
     <row r="34">
@@ -996,16 +996,16 @@
         </is>
       </c>
       <c r="B34">
-        <v>13.37059883050576</v>
+        <v>-189.2322378728478</v>
       </c>
       <c r="C34">
-        <v>28.42524124579148</v>
+        <v>110.6154248804475</v>
       </c>
       <c r="D34">
-        <v>0.4703776729594283</v>
+        <v>-1.710721972793297</v>
       </c>
       <c r="E34">
-        <v>0.638139688567269</v>
+        <v>0.08729715950855056</v>
       </c>
     </row>
     <row r="35">
@@ -1015,16 +1015,16 @@
         </is>
       </c>
       <c r="B35">
-        <v>-19.44279884209627</v>
+        <v>-288.9118621432233</v>
       </c>
       <c r="C35">
-        <v>28.42524124579347</v>
+        <v>110.6154248804552</v>
       </c>
       <c r="D35">
-        <v>-0.6839976721384391</v>
+        <v>-2.611858720928455</v>
       </c>
       <c r="E35">
-        <v>0.4940608006373368</v>
+        <v>0.009076706373553905</v>
       </c>
     </row>
     <row r="36">
@@ -1034,16 +1034,16 @@
         </is>
       </c>
       <c r="B36">
-        <v>540.7655669271422</v>
+        <v>933.3380919067628</v>
       </c>
       <c r="C36">
-        <v>28.42524124579539</v>
+        <v>110.6154248804627</v>
       </c>
       <c r="D36">
-        <v>19.02413289129538</v>
+        <v>8.437684824836872</v>
       </c>
       <c r="E36">
-        <v>5.969683727908709E-74</v>
+        <v>6.356589146139237E-17</v>
       </c>
     </row>
     <row r="37">
@@ -1053,16 +1053,16 @@
         </is>
       </c>
       <c r="B37">
-        <v>-33.29947551487844</v>
+        <v>-308.2082580790791</v>
       </c>
       <c r="C37">
-        <v>28.42524124579165</v>
+        <v>110.6154248804481</v>
       </c>
       <c r="D37">
-        <v>-1.171475563811034</v>
+        <v>-2.786304517766732</v>
       </c>
       <c r="E37">
-        <v>0.2415558845303881</v>
+        <v>0.005384725741520046</v>
       </c>
     </row>
     <row r="38">
@@ -1072,16 +1072,16 @@
         </is>
       </c>
       <c r="B38">
-        <v>251.0996820282764</v>
+        <v>68.37574814516199</v>
       </c>
       <c r="C38">
-        <v>28.32702233870495</v>
+        <v>110.2332108459306</v>
       </c>
       <c r="D38">
-        <v>8.864316165175731</v>
+        <v>0.6202826500330157</v>
       </c>
       <c r="E38">
-        <v>1.744115311109819E-18</v>
+        <v>0.5351467746071135</v>
       </c>
     </row>
     <row r="39">
@@ -1091,16 +1091,16 @@
         </is>
       </c>
       <c r="B39">
-        <v>11.60752424119112</v>
+        <v>-42.51822942460056</v>
       </c>
       <c r="C39">
-        <v>28.42524124579198</v>
+        <v>110.6154248804494</v>
       </c>
       <c r="D39">
-        <v>0.4083527081026789</v>
+        <v>-0.3843788465356733</v>
       </c>
       <c r="E39">
-        <v>0.6830611783174608</v>
+        <v>0.70074107961162</v>
       </c>
     </row>
     <row r="40">
@@ -1110,16 +1110,16 @@
         </is>
       </c>
       <c r="B40">
-        <v>368.6354018360266</v>
+        <v>330.9147188231822</v>
       </c>
       <c r="C40">
-        <v>28.32046230008419</v>
+        <v>110.2076827790624</v>
       </c>
       <c r="D40">
-        <v>13.01657430341208</v>
+        <v>3.00264655311354</v>
       </c>
       <c r="E40">
-        <v>3.751902553999794E-37</v>
+        <v>0.00271166480923321</v>
       </c>
     </row>
     <row r="41">
@@ -1129,16 +1129,16 @@
         </is>
       </c>
       <c r="B41">
-        <v>-33.58254914073378</v>
+        <v>-184.9899826153523</v>
       </c>
       <c r="C41">
-        <v>28.32046230008733</v>
+        <v>110.2076827790746</v>
       </c>
       <c r="D41">
-        <v>-1.185805118041107</v>
+        <v>-1.678557954858632</v>
       </c>
       <c r="E41">
-        <v>0.2358488805984822</v>
+        <v>0.09340415201044114</v>
       </c>
     </row>
     <row r="42">
@@ -1148,16 +1148,16 @@
         </is>
       </c>
       <c r="B42">
-        <v>-36.24485203030554</v>
+        <v>-270.8165240861492</v>
       </c>
       <c r="C42">
-        <v>28.32046230008572</v>
+        <v>110.2076827790683</v>
       </c>
       <c r="D42">
-        <v>-1.279811453861607</v>
+        <v>-2.457328901734111</v>
       </c>
       <c r="E42">
-        <v>0.2007691091764355</v>
+        <v>0.01408703336645721</v>
       </c>
     </row>
     <row r="43">
@@ -1167,16 +1167,16 @@
         </is>
       </c>
       <c r="B43">
-        <v>-31.39675570367498</v>
+        <v>-190.0644135919029</v>
       </c>
       <c r="C43">
-        <v>28.32046230008809</v>
+        <v>110.2076827790775</v>
       </c>
       <c r="D43">
-        <v>-1.108624406303471</v>
+        <v>-1.72460221283217</v>
       </c>
       <c r="E43">
-        <v>0.2677338203921892</v>
+        <v>0.08476328916963338</v>
       </c>
     </row>
     <row r="44">
@@ -1186,16 +1186,16 @@
         </is>
       </c>
       <c r="B44">
-        <v>-1.682525239228431</v>
+        <v>-100.3638921786717</v>
       </c>
       <c r="C44">
-        <v>28.32046230008905</v>
+        <v>110.2076827790813</v>
       </c>
       <c r="D44">
-        <v>-0.05941023212827782</v>
+        <v>-0.9106796336500228</v>
       </c>
       <c r="E44">
-        <v>0.9526316675361484</v>
+        <v>0.3625807574108506</v>
       </c>
     </row>
     <row r="45">
@@ -1205,16 +1205,16 @@
         </is>
       </c>
       <c r="B45">
-        <v>-2.129718446066662</v>
+        <v>27.31160800107498</v>
       </c>
       <c r="C45">
-        <v>28.32046230008942</v>
+        <v>110.2076827790827</v>
       </c>
       <c r="D45">
-        <v>-0.07520069494274947</v>
+        <v>0.2478194560702504</v>
       </c>
       <c r="E45">
-        <v>0.9400630195418711</v>
+        <v>0.8043011205553726</v>
       </c>
     </row>
     <row r="46">
@@ -1224,16 +1224,16 @@
         </is>
       </c>
       <c r="B46">
-        <v>-37.01772089448966</v>
+        <v>-192.6963404152731</v>
       </c>
       <c r="C46">
-        <v>28.32046230008773</v>
+        <v>110.2076827790762</v>
       </c>
       <c r="D46">
-        <v>-1.307101575611461</v>
+        <v>-1.748483731406955</v>
       </c>
       <c r="E46">
-        <v>0.1913378080820297</v>
+        <v>0.08054325250570983</v>
       </c>
     </row>
     <row r="47">
@@ -1243,16 +1243,16 @@
         </is>
       </c>
       <c r="B47">
-        <v>-31.24281964081756</v>
+        <v>-203.7996321938563</v>
       </c>
       <c r="C47">
-        <v>28.32702233870856</v>
+        <v>110.2332108459446</v>
       </c>
       <c r="D47">
-        <v>-1.102933420507266</v>
+        <v>-1.848804281666752</v>
       </c>
       <c r="E47">
-        <v>0.2701970171558167</v>
+        <v>0.06464274202451517</v>
       </c>
     </row>
     <row r="48">
@@ -1262,16 +1262,16 @@
         </is>
       </c>
       <c r="B48">
-        <v>-25.90828374686228</v>
+        <v>-211.5672928537165</v>
       </c>
       <c r="C48">
-        <v>28.32046230008678</v>
+        <v>110.2076827790725</v>
       </c>
       <c r="D48">
-        <v>-0.9148255940293349</v>
+        <v>-1.919714556360234</v>
       </c>
       <c r="E48">
-        <v>0.3604003265395757</v>
+        <v>0.05504490981981282</v>
       </c>
     </row>
     <row r="49">
@@ -1281,16 +1281,16 @@
         </is>
       </c>
       <c r="B49">
-        <v>-51.09066394180545</v>
+        <v>-306.3238097058927</v>
       </c>
       <c r="C49">
-        <v>28.42524124579201</v>
+        <v>110.6154248804495</v>
       </c>
       <c r="D49">
-        <v>-1.797369580790058</v>
+        <v>-2.769268481651272</v>
       </c>
       <c r="E49">
-        <v>0.07243713638621377</v>
+        <v>0.005673323037036744</v>
       </c>
     </row>
     <row r="50">
@@ -1300,16 +1300,16 @@
         </is>
       </c>
       <c r="B50">
-        <v>-40.64506072071595</v>
+        <v>-299.8522814805973</v>
       </c>
       <c r="C50">
-        <v>28.32046230008652</v>
+        <v>110.2076827790714</v>
       </c>
       <c r="D50">
-        <v>-1.435183518193903</v>
+        <v>-2.720792905896572</v>
       </c>
       <c r="E50">
-        <v>0.1514008828510464</v>
+        <v>0.006572474681289022</v>
       </c>
     </row>
     <row r="51">
@@ -1319,16 +1319,16 @@
         </is>
       </c>
       <c r="B51">
-        <v>-34.42699479758875</v>
+        <v>-260.8063090979441</v>
       </c>
       <c r="C51">
-        <v>28.32046230008789</v>
+        <v>110.2076827790768</v>
       </c>
       <c r="D51">
-        <v>-1.215622627653289</v>
+        <v>-2.366498437506926</v>
       </c>
       <c r="E51">
-        <v>0.2242810928705721</v>
+        <v>0.01805794541321708</v>
       </c>
     </row>
     <row r="52">
@@ -1338,16 +1338,16 @@
         </is>
       </c>
       <c r="B52">
-        <v>-42.23925679603148</v>
+        <v>-292.5111682314712</v>
       </c>
       <c r="C52">
-        <v>28.3204623000891</v>
+        <v>110.2076827790815</v>
       </c>
       <c r="D52">
-        <v>-1.49147483358344</v>
+        <v>-2.654181277160404</v>
       </c>
       <c r="E52">
-        <v>0.136004374704092</v>
+        <v>0.008017026052473886</v>
       </c>
     </row>
     <row r="53">
@@ -1357,16 +1357,16 @@
         </is>
       </c>
       <c r="B53">
-        <v>-27.57617098342799</v>
+        <v>-249.3056121628904</v>
       </c>
       <c r="C53">
-        <v>28.32046230009053</v>
+        <v>110.207682779087</v>
       </c>
       <c r="D53">
-        <v>-0.9737189559698624</v>
+        <v>-2.262143671622488</v>
       </c>
       <c r="E53">
-        <v>0.3303211690691568</v>
+        <v>0.0238020818208933</v>
       </c>
     </row>
     <row r="54">
@@ -1376,16 +1376,16 @@
         </is>
       </c>
       <c r="B54">
-        <v>-44.67894711518996</v>
+        <v>-291.6215936266952</v>
       </c>
       <c r="C54">
-        <v>28.32046230008888</v>
+        <v>110.2076827790806</v>
       </c>
       <c r="D54">
-        <v>-1.577620684357604</v>
+        <v>-2.64610947506511</v>
       </c>
       <c r="E54">
-        <v>0.1148207467809845</v>
+        <v>0.008210136085106694</v>
       </c>
     </row>
     <row r="55">
@@ -1395,16 +1395,16 @@
         </is>
       </c>
       <c r="B55">
-        <v>-43.81662904864952</v>
+        <v>-296.1009133706013</v>
       </c>
       <c r="C55">
-        <v>28.32046230008868</v>
+        <v>110.2076827790798</v>
       </c>
       <c r="D55">
-        <v>-1.547172097134598</v>
+        <v>-2.686753826084515</v>
       </c>
       <c r="E55">
-        <v>0.1219897926666592</v>
+        <v>0.007278455176439903</v>
       </c>
     </row>
     <row r="56">
@@ -1414,16 +1414,16 @@
         </is>
       </c>
       <c r="B56">
-        <v>-43.8817146822885</v>
+        <v>-306.683837925742</v>
       </c>
       <c r="C56">
-        <v>28.32046230008725</v>
+        <v>110.2076827790743</v>
       </c>
       <c r="D56">
-        <v>-1.549470281145562</v>
+        <v>-2.782780929534014</v>
       </c>
       <c r="E56">
-        <v>0.121436754135369</v>
+        <v>0.005443305006643197</v>
       </c>
     </row>
     <row r="57">
@@ -1433,16 +1433,16 @@
         </is>
       </c>
       <c r="B57">
-        <v>-49.58189771953459</v>
+        <v>-333.6801392204912</v>
       </c>
       <c r="C57">
-        <v>28.32046230008491</v>
+        <v>110.2076827790652</v>
       </c>
       <c r="D57">
-        <v>-1.750744645131938</v>
+        <v>-3.027739362685125</v>
       </c>
       <c r="E57">
-        <v>0.08015274143703793</v>
+        <v>0.002497347221623921</v>
       </c>
     </row>
     <row r="58">
@@ -1452,16 +1452,16 @@
         </is>
       </c>
       <c r="B58">
-        <v>-45.94633748978116</v>
+        <v>-323.9100450089665</v>
       </c>
       <c r="C58">
-        <v>28.32046230008526</v>
+        <v>110.2076827790665</v>
       </c>
       <c r="D58">
-        <v>-1.622372438801708</v>
+        <v>-2.939087700975524</v>
       </c>
       <c r="E58">
-        <v>0.104891028247121</v>
+        <v>0.003331870049670612</v>
       </c>
     </row>
     <row r="59">
@@ -1471,16 +1471,16 @@
         </is>
       </c>
       <c r="B59">
-        <v>-21.09772788154014</v>
+        <v>-181.2685655970425</v>
       </c>
       <c r="C59">
-        <v>28.32046230008635</v>
+        <v>110.2076827790708</v>
       </c>
       <c r="D59">
-        <v>-0.7449641060935581</v>
+        <v>-1.644790644590767</v>
       </c>
       <c r="E59">
-        <v>0.4563863866185451</v>
+        <v>0.1001799050504775</v>
       </c>
     </row>
     <row r="60">
@@ -1490,16 +1490,16 @@
         </is>
       </c>
       <c r="B60">
-        <v>-48.01830379539803</v>
+        <v>-330.9860745735949</v>
       </c>
       <c r="C60">
-        <v>28.32046230008773</v>
+        <v>110.2076827790761</v>
       </c>
       <c r="D60">
-        <v>-1.695533896537038</v>
+        <v>-3.003294019320724</v>
       </c>
       <c r="E60">
-        <v>0.09013950249503112</v>
+        <v>0.002705929733526745</v>
       </c>
     </row>
     <row r="61">
@@ -1509,16 +1509,16 @@
         </is>
       </c>
       <c r="B61">
-        <v>-39.23774852382459</v>
+        <v>-232.9022885917071</v>
       </c>
       <c r="C61">
-        <v>28.32046230008558</v>
+        <v>110.2076827790678</v>
       </c>
       <c r="D61">
-        <v>-1.385491102089319</v>
+        <v>-2.113303562135536</v>
       </c>
       <c r="E61">
-        <v>0.1660664351088785</v>
+        <v>0.03470603036011006</v>
       </c>
     </row>
     <row r="62">
@@ -1528,16 +1528,16 @@
         </is>
       </c>
       <c r="B62">
-        <v>-47.87732229299924</v>
+        <v>-323.9308829559847</v>
       </c>
       <c r="C62">
-        <v>28.32046230008532</v>
+        <v>110.2076827790668</v>
       </c>
       <c r="D62">
-        <v>-1.690555817404683</v>
+        <v>-2.939276779871768</v>
       </c>
       <c r="E62">
-        <v>0.09108717211032485</v>
+        <v>0.003329847349137708</v>
       </c>
     </row>
     <row r="63">
@@ -1547,16 +1547,16 @@
         </is>
       </c>
       <c r="B63">
-        <v>-50.91850702336914</v>
+        <v>-329.6588751035973</v>
       </c>
       <c r="C63">
-        <v>28.32046230008649</v>
+        <v>110.2076827790713</v>
       </c>
       <c r="D63">
-        <v>-1.797940530907705</v>
+        <v>-2.991251306539586</v>
       </c>
       <c r="E63">
-        <v>0.07234656634802895</v>
+        <v>0.002814437132456235</v>
       </c>
     </row>
     <row r="64">
@@ -1566,16 +1566,16 @@
         </is>
       </c>
       <c r="B64">
-        <v>-40.07794636338762</v>
+        <v>-255.9317701241094</v>
       </c>
       <c r="C64">
-        <v>28.32046230008977</v>
+        <v>110.2076827790841</v>
       </c>
       <c r="D64">
-        <v>-1.415158620601351</v>
+        <v>-2.322267955103778</v>
       </c>
       <c r="E64">
-        <v>0.1571873474097982</v>
+        <v>0.02032466629876428</v>
       </c>
     </row>
     <row r="65">
@@ -1585,16 +1585,16 @@
         </is>
       </c>
       <c r="B65">
-        <v>-31.97706974927024</v>
+        <v>-84.46976382465658</v>
       </c>
       <c r="C65">
-        <v>28.32046230009057</v>
+        <v>110.2076827790872</v>
       </c>
       <c r="D65">
-        <v>-1.129115386974738</v>
+        <v>-0.7664598483027485</v>
       </c>
       <c r="E65">
-        <v>0.2589929840219941</v>
+        <v>0.4434988087923998</v>
       </c>
     </row>
     <row r="66">
@@ -1604,16 +1604,16 @@
         </is>
       </c>
       <c r="B66">
-        <v>-22.27829773668577</v>
+        <v>108.2214538353215</v>
       </c>
       <c r="C66">
-        <v>28.32046230008863</v>
+        <v>110.2076827790796</v>
       </c>
       <c r="D66">
-        <v>-0.7866502142733753</v>
+        <v>0.981977400362008</v>
       </c>
       <c r="E66">
-        <v>0.4315856446468507</v>
+        <v>0.3262371319872113</v>
       </c>
     </row>
     <row r="67">
@@ -1623,16 +1623,16 @@
         </is>
       </c>
       <c r="B67">
-        <v>-25.66138187539357</v>
+        <v>-213.1486294696175</v>
       </c>
       <c r="C67">
-        <v>28.32046230008936</v>
+        <v>110.2076827790825</v>
       </c>
       <c r="D67">
-        <v>-0.9061074499236758</v>
+        <v>-1.934063253075432</v>
       </c>
       <c r="E67">
-        <v>0.3649949105493355</v>
+        <v>0.05325502594780941</v>
       </c>
     </row>
     <row r="68">
@@ -1642,16 +1642,16 @@
         </is>
       </c>
       <c r="B68">
-        <v>-50.16837732098162</v>
+        <v>-320.0934784414327</v>
       </c>
       <c r="C68">
-        <v>28.32046230008697</v>
+        <v>110.2076827790732</v>
       </c>
       <c r="D68">
-        <v>-1.771453332554799</v>
+        <v>-2.904457024861915</v>
       </c>
       <c r="E68">
-        <v>0.0766470608175694</v>
+        <v>0.003721794385816417</v>
       </c>
     </row>
     <row r="69">
@@ -1661,16 +1661,16 @@
         </is>
       </c>
       <c r="B69">
-        <v>-50.35859494228425</v>
+        <v>-318.3616656874647</v>
       </c>
       <c r="C69">
-        <v>28.42524124579291</v>
+        <v>110.615424880453</v>
       </c>
       <c r="D69">
-        <v>-1.771615393052736</v>
+        <v>-2.878094678310301</v>
       </c>
       <c r="E69">
-        <v>0.07662012782185017</v>
+        <v>0.004045967320367022</v>
       </c>
     </row>
     <row r="70">
@@ -1680,16 +1680,16 @@
         </is>
       </c>
       <c r="B70">
-        <v>-35.65870628277636</v>
+        <v>-229.7970322181357</v>
       </c>
       <c r="C70">
-        <v>28.42524124579412</v>
+        <v>110.6154248804577</v>
       </c>
       <c r="D70">
-        <v>-1.254473303302308</v>
+        <v>-2.077441120589445</v>
       </c>
       <c r="E70">
-        <v>0.2098257140511663</v>
+        <v>0.03789611005352446</v>
       </c>
     </row>
     <row r="71">
@@ -1699,16 +1699,16 @@
         </is>
       </c>
       <c r="B71">
-        <v>-46.16208563941256</v>
+        <v>-306.4956081672203</v>
       </c>
       <c r="C71">
-        <v>28.32046230008696</v>
+        <v>110.2076827790732</v>
       </c>
       <c r="D71">
-        <v>-1.629990540065118</v>
+        <v>-2.781072974573234</v>
       </c>
       <c r="E71">
-        <v>0.1032707469217156</v>
+        <v>0.005471906225648706</v>
       </c>
     </row>
     <row r="72">
@@ -1718,16 +1718,16 @@
         </is>
       </c>
       <c r="B72">
-        <v>-48.50547033878851</v>
+        <v>-301.5637634018157</v>
       </c>
       <c r="C72">
-        <v>28.32702233870566</v>
+        <v>110.2332108459333</v>
       </c>
       <c r="D72">
-        <v>-1.71233918478298</v>
+        <v>-2.735688828145395</v>
       </c>
       <c r="E72">
-        <v>0.08699882139816061</v>
+        <v>0.006283397847164512</v>
       </c>
     </row>
     <row r="73">
@@ -1737,16 +1737,16 @@
         </is>
       </c>
       <c r="B73">
-        <v>-47.94879183250256</v>
+        <v>-320.4052096501752</v>
       </c>
       <c r="C73">
-        <v>28.32046230008567</v>
+        <v>110.2076827790681</v>
       </c>
       <c r="D73">
-        <v>-1.693079418140625</v>
+        <v>-2.907285604511685</v>
       </c>
       <c r="E73">
-        <v>0.09060576075544544</v>
+        <v>0.003688454131307176</v>
       </c>
     </row>
     <row r="74">
@@ -1756,16 +1756,16 @@
         </is>
       </c>
       <c r="B74">
-        <v>250.8326312575797</v>
+        <v>304.8077436631041</v>
       </c>
       <c r="C74">
-        <v>28.3270223387055</v>
+        <v>110.2332108459327</v>
       </c>
       <c r="D74">
-        <v>8.854888743983755</v>
+        <v>2.765117166813894</v>
       </c>
       <c r="E74">
-        <v>1.891602436190449E-18</v>
+        <v>0.00574573109225981</v>
       </c>
     </row>
     <row r="75">
@@ -1775,16 +1775,16 @@
         </is>
       </c>
       <c r="B75">
-        <v>0.09185187858310406</v>
+        <v>-141.1163632824512</v>
       </c>
       <c r="C75">
-        <v>28.32702233870882</v>
+        <v>110.2332108459456</v>
       </c>
       <c r="D75">
-        <v>0.003242553258327778</v>
+        <v>-1.280161960261375</v>
       </c>
       <c r="E75">
-        <v>0.9974131648224439</v>
+        <v>0.2006458618422212</v>
       </c>
     </row>
     <row r="76">
@@ -1794,16 +1794,16 @@
         </is>
       </c>
       <c r="B76">
-        <v>16.95204853712022</v>
+        <v>135.5217431380437</v>
       </c>
       <c r="C76">
-        <v>28.32702233870517</v>
+        <v>110.2332108459315</v>
       </c>
       <c r="D76">
-        <v>0.5984408927428091</v>
+        <v>1.229409377609956</v>
       </c>
       <c r="E76">
-        <v>0.5496177627910206</v>
+        <v>0.2190719527128503</v>
       </c>
     </row>
     <row r="77">
@@ -1813,16 +1813,16 @@
         </is>
       </c>
       <c r="B77">
-        <v>-40.69642090375726</v>
+        <v>-287.0805879958806</v>
       </c>
       <c r="C77">
-        <v>28.32702233870704</v>
+        <v>110.2332108459387</v>
       </c>
       <c r="D77">
-        <v>-1.436664271208917</v>
+        <v>-2.604302149894761</v>
       </c>
       <c r="E77">
-        <v>0.1509795344194506</v>
+        <v>0.009278560613251873</v>
       </c>
     </row>
     <row r="78">
@@ -1832,16 +1832,16 @@
         </is>
       </c>
       <c r="B78">
-        <v>-27.5801257361035</v>
+        <v>-246.4491583327814</v>
       </c>
       <c r="C78">
-        <v>28.32702233870673</v>
+        <v>110.2332108459375</v>
       </c>
       <c r="D78">
-        <v>-0.9736330704416236</v>
+        <v>-2.235706974708557</v>
       </c>
       <c r="E78">
-        <v>0.3303638151913663</v>
+        <v>0.02548775175232126</v>
       </c>
     </row>
     <row r="79">
@@ -1851,16 +1851,16 @@
         </is>
       </c>
       <c r="B79">
-        <v>-31.81405598040287</v>
+        <v>-226.1248628265446</v>
       </c>
       <c r="C79">
-        <v>28.32702233870776</v>
+        <v>110.2332108459415</v>
       </c>
       <c r="D79">
-        <v>-1.123099194825367</v>
+        <v>-2.051331546012659</v>
       </c>
       <c r="E79">
-        <v>0.2615385392538924</v>
+        <v>0.04037274866115255</v>
       </c>
     </row>
     <row r="80">
@@ -1870,16 +1870,16 @@
         </is>
       </c>
       <c r="B80">
-        <v>-38.32937712343242</v>
+        <v>-288.7807733659214</v>
       </c>
       <c r="C80">
-        <v>28.32702233870424</v>
+        <v>110.2332108459278</v>
       </c>
       <c r="D80">
-        <v>-1.35310293701649</v>
+        <v>-2.619725681124796</v>
       </c>
       <c r="E80">
-        <v>0.176185172407183</v>
+        <v>0.008870738390250831</v>
       </c>
     </row>
     <row r="81">
@@ -1889,16 +1889,16 @@
         </is>
       </c>
       <c r="B81">
-        <v>-3.564870091909087</v>
+        <v>-156.555335195041</v>
       </c>
       <c r="C81">
-        <v>28.32702233870766</v>
+        <v>110.2332108459411</v>
       </c>
       <c r="D81">
-        <v>-0.1258469756998724</v>
+        <v>-1.420219314974308</v>
       </c>
       <c r="E81">
-        <v>0.8998664908272203</v>
+        <v>0.155709388257131</v>
       </c>
     </row>
     <row r="82">
@@ -1908,16 +1908,16 @@
         </is>
       </c>
       <c r="B82">
-        <v>-44.37899797794044</v>
+        <v>-304.2825900918559</v>
       </c>
       <c r="C82">
-        <v>28.32702233870491</v>
+        <v>110.2332108459304</v>
       </c>
       <c r="D82">
-        <v>-1.566666536542486</v>
+        <v>-2.760353143637832</v>
       </c>
       <c r="E82">
-        <v>0.1173606808904464</v>
+        <v>0.005829853116517855</v>
       </c>
     </row>
     <row r="83">
@@ -1927,16 +1927,16 @@
         </is>
       </c>
       <c r="B83">
-        <v>-30.42709255487261</v>
+        <v>-271.8294337527637</v>
       </c>
       <c r="C83">
-        <v>28.32046230008819</v>
+        <v>110.2076827790779</v>
       </c>
       <c r="D83">
-        <v>-1.074385447259378</v>
+        <v>-2.466519818746869</v>
       </c>
       <c r="E83">
-        <v>0.2827876142773337</v>
+        <v>0.01373179502302058</v>
       </c>
     </row>
     <row r="84">
@@ -1946,16 +1946,16 @@
         </is>
       </c>
       <c r="B84">
-        <v>51.33010049391196</v>
+        <v>-22.30724375087122</v>
       </c>
       <c r="C84">
-        <v>28.42524124579167</v>
+        <v>110.6154248804482</v>
       </c>
       <c r="D84">
-        <v>1.805792958802463</v>
+        <v>-0.2016648561896373</v>
       </c>
       <c r="E84">
-        <v>0.07111032070854015</v>
+        <v>0.8402005214720683</v>
       </c>
     </row>
     <row r="85">
@@ -1965,16 +1965,16 @@
         </is>
       </c>
       <c r="B85">
-        <v>-45.81998941652788</v>
+        <v>-321.6280503835144</v>
       </c>
       <c r="C85">
-        <v>28.42524124579212</v>
+        <v>110.61542488045</v>
       </c>
       <c r="D85">
-        <v>-1.611947248585296</v>
+        <v>-2.907623875522975</v>
       </c>
       <c r="E85">
-        <v>0.1071410018272403</v>
+        <v>0.003684485202913243</v>
       </c>
     </row>
     <row r="86">
@@ -1984,16 +1984,16 @@
         </is>
       </c>
       <c r="B86">
-        <v>-43.5702549213032</v>
+        <v>-288.0153719545622</v>
       </c>
       <c r="C86">
-        <v>28.32046230008839</v>
+        <v>110.2076827790787</v>
       </c>
       <c r="D86">
-        <v>-1.538472587757411</v>
+        <v>-2.613387421745498</v>
       </c>
       <c r="E86">
-        <v>0.12410111916731</v>
+        <v>0.009036351506689614</v>
       </c>
     </row>
     <row r="87">
@@ -2003,16 +2003,16 @@
         </is>
       </c>
       <c r="B87">
-        <v>-50.93149229008655</v>
+        <v>-336.9686954081973</v>
       </c>
       <c r="C87">
-        <v>28.42524124579221</v>
+        <v>110.6154248804503</v>
       </c>
       <c r="D87">
-        <v>-1.79176992200993</v>
+        <v>-3.046308376723975</v>
       </c>
       <c r="E87">
-        <v>0.07333034523894882</v>
+        <v>0.002348859745238311</v>
       </c>
     </row>
     <row r="88">
@@ -2022,16 +2022,16 @@
         </is>
       </c>
       <c r="B88">
-        <v>76.88509653273495</v>
+        <v>-21.06405910327422</v>
       </c>
       <c r="C88">
-        <v>28.4252412457928</v>
+        <v>110.6154248804526</v>
       </c>
       <c r="D88">
-        <v>2.704817731111241</v>
+        <v>-0.1904260560951527</v>
       </c>
       <c r="E88">
-        <v>0.00689574844604808</v>
+        <v>0.8489958082403658</v>
       </c>
     </row>
     <row r="89">
@@ -2041,16 +2041,16 @@
         </is>
       </c>
       <c r="B89">
-        <v>-9.347055736858104</v>
+        <v>-264.5696654377987</v>
       </c>
       <c r="C89">
-        <v>28.42524124579359</v>
+        <v>110.6154248804557</v>
       </c>
       <c r="D89">
-        <v>-0.3288294250885662</v>
+        <v>-2.391797217465145</v>
       </c>
       <c r="E89">
-        <v>0.7423211869230162</v>
+        <v>0.01686368375511363</v>
       </c>
     </row>
     <row r="90">
@@ -2060,16 +2060,16 @@
         </is>
       </c>
       <c r="B90">
-        <v>0.9085909395619098</v>
+        <v>-237.3165986932999</v>
       </c>
       <c r="C90">
-        <v>28.42524124579144</v>
+        <v>110.6154248804473</v>
       </c>
       <c r="D90">
-        <v>0.03196422966846177</v>
+        <v>-2.145420486788264</v>
       </c>
       <c r="E90">
-        <v>0.9745039644593136</v>
+        <v>0.03204678663740287</v>
       </c>
     </row>
     <row r="91">
@@ -2079,16 +2079,16 @@
         </is>
       </c>
       <c r="B91">
-        <v>5.415321554626996</v>
+        <v>256.7741206182364</v>
       </c>
       <c r="C91">
-        <v>28.42524124579308</v>
+        <v>110.6154248804537</v>
       </c>
       <c r="D91">
-        <v>0.190511014763277</v>
+        <v>2.321322915820664</v>
       </c>
       <c r="E91">
-        <v>0.8489292490141349</v>
+        <v>0.02037569340567489</v>
       </c>
     </row>
     <row r="92">
@@ -2098,16 +2098,16 @@
         </is>
       </c>
       <c r="B92">
-        <v>-3.068608756711265</v>
+        <v>-214.8388199457463</v>
       </c>
       <c r="C92">
-        <v>28.42524124579083</v>
+        <v>110.6154248804449</v>
       </c>
       <c r="D92">
-        <v>-0.1079536574615936</v>
+        <v>-1.942213937865789</v>
       </c>
       <c r="E92">
-        <v>0.9140439543825296</v>
+        <v>0.05226014352029879</v>
       </c>
     </row>
     <row r="93">
@@ -2117,16 +2117,16 @@
         </is>
       </c>
       <c r="B93">
-        <v>85.18241908128009</v>
+        <v>102.1462152084655</v>
       </c>
       <c r="C93">
-        <v>28.4252412457924</v>
+        <v>110.615424880451</v>
       </c>
       <c r="D93">
-        <v>2.99671754215592</v>
+        <v>0.9234355454391761</v>
       </c>
       <c r="E93">
-        <v>0.002764701599611479</v>
+        <v>0.3558985863538952</v>
       </c>
     </row>
     <row r="94">
@@ -2136,16 +2136,16 @@
         </is>
       </c>
       <c r="B94">
-        <v>-22.55644131491035</v>
+        <v>-263.6327630116674</v>
       </c>
       <c r="C94">
-        <v>28.42524124579354</v>
+        <v>110.6154248804555</v>
       </c>
       <c r="D94">
-        <v>-0.7935356157530702</v>
+        <v>-2.383327309880888</v>
       </c>
       <c r="E94">
-        <v>0.427565808389576</v>
+        <v>0.01725555455170776</v>
       </c>
     </row>
     <row r="95">
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="B95">
-        <v>379.0493392472338</v>
+        <v>925.6064117561292</v>
       </c>
       <c r="C95">
-        <v>29.2723057229976</v>
+        <v>113.9117345313343</v>
       </c>
       <c r="D95">
-        <v>12.94907694782089</v>
+        <v>8.125645839424189</v>
       </c>
       <c r="E95">
-        <v>8.425682660051348E-37</v>
+        <v>7.969277495977671E-16</v>
       </c>
     </row>
     <row r="96">
@@ -2174,16 +2174,16 @@
         </is>
       </c>
       <c r="B96">
-        <v>17.2138414525331</v>
+        <v>26.98535789166553</v>
       </c>
       <c r="C96">
-        <v>29.27230572299645</v>
+        <v>113.9117345313298</v>
       </c>
       <c r="D96">
-        <v>0.5880589529033866</v>
+        <v>0.2368970852975959</v>
       </c>
       <c r="E96">
-        <v>0.556563242018463</v>
+        <v>0.8127623995714748</v>
       </c>
     </row>
     <row r="97">
@@ -2193,16 +2193,16 @@
         </is>
       </c>
       <c r="B97">
-        <v>-13.6757196430595</v>
+        <v>-263.2920595636842</v>
       </c>
       <c r="C97">
-        <v>28.327022338708</v>
+        <v>110.2332108459424</v>
       </c>
       <c r="D97">
-        <v>-0.482779992882346</v>
+        <v>-2.388500321664863</v>
       </c>
       <c r="E97">
-        <v>0.6293080786371738</v>
+        <v>0.01701527969475733</v>
       </c>
     </row>
     <row r="98">
@@ -2212,16 +2212,16 @@
         </is>
       </c>
       <c r="B98">
-        <v>-26.7463058327858</v>
+        <v>-261.8415824345802</v>
       </c>
       <c r="C98">
-        <v>28.42524124579367</v>
+        <v>110.615424880456</v>
       </c>
       <c r="D98">
-        <v>-0.9409350514041348</v>
+        <v>-2.367134445467772</v>
       </c>
       <c r="E98">
-        <v>0.3468588348039729</v>
+        <v>0.01802703634003361</v>
       </c>
     </row>
     <row r="99">
@@ -2231,16 +2231,16 @@
         </is>
       </c>
       <c r="B99">
-        <v>-17.24908855348237</v>
+        <v>-284.1372948194694</v>
       </c>
       <c r="C99">
-        <v>28.42524124579149</v>
+        <v>110.6154248804475</v>
       </c>
       <c r="D99">
-        <v>-0.6068229431838575</v>
+        <v>-2.568695054297927</v>
       </c>
       <c r="E99">
-        <v>0.5440415766526091</v>
+        <v>0.01028466621758786</v>
       </c>
     </row>
     <row r="100">
@@ -2250,16 +2250,16 @@
         </is>
       </c>
       <c r="B100">
-        <v>-21.23825203228214</v>
+        <v>-209.4213703105958</v>
       </c>
       <c r="C100">
-        <v>28.42524124579362</v>
+        <v>110.6154248804558</v>
       </c>
       <c r="D100">
-        <v>-0.7471617161886002</v>
+        <v>-1.893238402663295</v>
       </c>
       <c r="E100">
-        <v>0.4550592354646812</v>
+        <v>0.05847936521058554</v>
       </c>
     </row>
     <row r="101">
@@ -2269,16 +2269,16 @@
         </is>
       </c>
       <c r="B101">
-        <v>-20.44840953887698</v>
+        <v>-151.383611649983</v>
       </c>
       <c r="C101">
-        <v>28.32046230008783</v>
+        <v>110.2076827790765</v>
       </c>
       <c r="D101">
-        <v>-0.7220365727862275</v>
+        <v>-1.373621219796882</v>
       </c>
       <c r="E101">
-        <v>0.470361644873023</v>
+        <v>0.1697228142207462</v>
       </c>
     </row>
     <row r="102">
@@ -2288,16 +2288,16 @@
         </is>
       </c>
       <c r="B102">
-        <v>310.4102948353002</v>
+        <v>190.1502465620174</v>
       </c>
       <c r="C102">
-        <v>28.32702233870688</v>
+        <v>110.2332108459381</v>
       </c>
       <c r="D102">
-        <v>10.95809828240035</v>
+        <v>1.724981474301527</v>
       </c>
       <c r="E102">
-        <v>3.932593232180174E-27</v>
+        <v>0.08469489875035514</v>
       </c>
     </row>
     <row r="103">
@@ -2307,16 +2307,16 @@
         </is>
       </c>
       <c r="B103">
-        <v>26.43617432328726</v>
+        <v>-218.1194290766889</v>
       </c>
       <c r="C103">
-        <v>28.32702233870537</v>
+        <v>110.2332108459322</v>
       </c>
       <c r="D103">
-        <v>0.9332493195786942</v>
+        <v>-1.978708842850856</v>
       </c>
       <c r="E103">
-        <v>0.350810904946519</v>
+        <v>0.0479942972638536</v>
       </c>
     </row>
     <row r="104">
@@ -2326,16 +2326,16 @@
         </is>
       </c>
       <c r="B104">
-        <v>21.96115678670052</v>
+        <v>-158.8956741118378</v>
       </c>
       <c r="C104">
-        <v>28.32702233870649</v>
+        <v>110.2332108459366</v>
       </c>
       <c r="D104">
-        <v>0.7752723362205441</v>
+        <v>-1.441450111926002</v>
       </c>
       <c r="E104">
-        <v>0.4382760999201102</v>
+        <v>0.1496238381353065</v>
       </c>
     </row>
     <row r="105">
@@ -2345,16 +2345,16 @@
         </is>
       </c>
       <c r="B105">
-        <v>-25.69869036409385</v>
+        <v>-286.8637503491556</v>
       </c>
       <c r="C105">
-        <v>28.32702233870696</v>
+        <v>110.2332108459384</v>
       </c>
       <c r="D105">
-        <v>-0.9072146749776213</v>
+        <v>-2.602335068966425</v>
       </c>
       <c r="E105">
-        <v>0.3644093659209535</v>
+        <v>0.009331759426218828</v>
       </c>
     </row>
     <row r="106">
@@ -2364,16 +2364,16 @@
         </is>
       </c>
       <c r="B106">
-        <v>-24.99585139839736</v>
+        <v>-226.0727135873043</v>
       </c>
       <c r="C106">
-        <v>28.32702233870603</v>
+        <v>110.2332108459348</v>
       </c>
       <c r="D106">
-        <v>-0.8824030672734366</v>
+        <v>-2.050858464998087</v>
       </c>
       <c r="E106">
-        <v>0.377671507230227</v>
+        <v>0.04041886086616725</v>
       </c>
     </row>
     <row r="107">
@@ -2383,16 +2383,16 @@
         </is>
       </c>
       <c r="B107">
-        <v>-6.475434690183255</v>
+        <v>-252.9410476427106</v>
       </c>
       <c r="C107">
-        <v>28.32702233870786</v>
+        <v>110.2332108459419</v>
       </c>
       <c r="D107">
-        <v>-0.2285956713965946</v>
+        <v>-2.294599292732316</v>
       </c>
       <c r="E107">
-        <v>0.8192080115161883</v>
+        <v>0.02186566550713868</v>
       </c>
     </row>
     <row r="108">
@@ -2402,16 +2402,16 @@
         </is>
       </c>
       <c r="B108">
-        <v>-3.489869858898575</v>
+        <v>-262.0589025314505</v>
       </c>
       <c r="C108">
-        <v>28.42524124579277</v>
+        <v>110.6154248804525</v>
       </c>
       <c r="D108">
-        <v>-0.1227736232287954</v>
+        <v>-2.369099090969189</v>
       </c>
       <c r="E108">
-        <v>0.9022994635974223</v>
+        <v>0.01793185009185657</v>
       </c>
     </row>
     <row r="109">
@@ -2421,16 +2421,16 @@
         </is>
       </c>
       <c r="B109">
-        <v>-16.61379798799378</v>
+        <v>-287.1767579706406</v>
       </c>
       <c r="C109">
-        <v>28.32702233870457</v>
+        <v>110.2332108459291</v>
       </c>
       <c r="D109">
-        <v>-0.586499978336712</v>
+        <v>-2.60517457277029</v>
       </c>
       <c r="E109">
-        <v>0.5576098764602466</v>
+        <v>0.009255053152031886</v>
       </c>
     </row>
     <row r="110">
@@ -2440,16 +2440,16 @@
         </is>
       </c>
       <c r="B110">
-        <v>-11.89385214764824</v>
+        <v>-283.80731123735</v>
       </c>
       <c r="C110">
-        <v>28.42524124579258</v>
+        <v>110.6154248804518</v>
       </c>
       <c r="D110">
-        <v>-0.4184257239825092</v>
+        <v>-2.565711893653858</v>
       </c>
       <c r="E110">
-        <v>0.6756835980476937</v>
+        <v>0.01037321522128687</v>
       </c>
     </row>
     <row r="111">
@@ -2459,16 +2459,16 @@
         </is>
       </c>
       <c r="B111">
-        <v>-17.08589880623344</v>
+        <v>-278.5771990916237</v>
       </c>
       <c r="C111">
-        <v>28.32702233870738</v>
+        <v>110.23321084594</v>
       </c>
       <c r="D111">
-        <v>-0.6031660723791099</v>
+        <v>-2.52716215878859</v>
       </c>
       <c r="E111">
-        <v>0.5464708562809335</v>
+        <v>0.01158010054178077</v>
       </c>
     </row>
     <row r="112">
@@ -2478,16 +2478,16 @@
         </is>
       </c>
       <c r="B112">
-        <v>-39.97862461998011</v>
+        <v>-315.8391428281528</v>
       </c>
       <c r="C112">
-        <v>28.32702233870698</v>
+        <v>110.2332108459385</v>
       </c>
       <c r="D112">
-        <v>-1.411324640548329</v>
+        <v>-2.8651904485443</v>
       </c>
       <c r="E112">
-        <v>0.1583141151854822</v>
+        <v>0.004213820214084987</v>
       </c>
     </row>
     <row r="113">
@@ -2497,16 +2497,16 @@
         </is>
       </c>
       <c r="B113">
-        <v>171.5840614915371</v>
+        <v>65.83264476033541</v>
       </c>
       <c r="C113">
-        <v>28.32046230008816</v>
+        <v>110.2076827790778</v>
       </c>
       <c r="D113">
-        <v>6.058660330943927</v>
+        <v>0.5973507753747392</v>
       </c>
       <c r="E113">
-        <v>1.653431861534401E-09</v>
+        <v>0.5503450335428045</v>
       </c>
     </row>
     <row r="114">
@@ -2516,16 +2516,16 @@
         </is>
       </c>
       <c r="B114">
-        <v>-5.744829930574069</v>
+        <v>-264.0293857580181</v>
       </c>
       <c r="C114">
-        <v>28.32046230008877</v>
+        <v>110.2076827790802</v>
       </c>
       <c r="D114">
-        <v>-0.202850852846285</v>
+        <v>-2.395743918210179</v>
       </c>
       <c r="E114">
-        <v>0.8392735249398194</v>
+        <v>0.01668377016182079</v>
       </c>
     </row>
     <row r="115">
@@ -2535,16 +2535,16 @@
         </is>
       </c>
       <c r="B115">
-        <v>-9.474416299369731</v>
+        <v>-208.8123187540674</v>
       </c>
       <c r="C115">
-        <v>28.32702233870623</v>
+        <v>110.2332108459355</v>
       </c>
       <c r="D115">
-        <v>-0.3344656627189448</v>
+        <v>-1.894277751247837</v>
       </c>
       <c r="E115">
-        <v>0.7380654462740899</v>
+        <v>0.05834125946523178</v>
       </c>
     </row>
     <row r="116">
@@ -2554,16 +2554,16 @@
         </is>
       </c>
       <c r="B116">
-        <v>175.3569117134691</v>
+        <v>775.3741608369887</v>
       </c>
       <c r="C116">
-        <v>28.32702233870681</v>
+        <v>110.2332108459378</v>
       </c>
       <c r="D116">
-        <v>6.190446338366342</v>
+        <v>7.033943354155342</v>
       </c>
       <c r="E116">
-        <v>7.344807152575823E-10</v>
+        <v>2.799091724326093E-12</v>
       </c>
     </row>
     <row r="117">
@@ -2573,16 +2573,16 @@
         </is>
       </c>
       <c r="B117">
-        <v>-43.48070312500636</v>
+        <v>-334.7798410008123</v>
       </c>
       <c r="C117">
-        <v>28.42524124579336</v>
+        <v>110.6154248804548</v>
       </c>
       <c r="D117">
-        <v>-1.529651155781872</v>
+        <v>-3.026520409451199</v>
       </c>
       <c r="E117">
-        <v>0.1262710640051408</v>
+        <v>0.002507388973108235</v>
       </c>
     </row>
     <row r="118">
@@ -2592,16 +2592,16 @@
         </is>
       </c>
       <c r="B118">
-        <v>-36.70713465108719</v>
+        <v>-262.4725526577548</v>
       </c>
       <c r="C118">
-        <v>28.32702233870582</v>
+        <v>110.2332108459339</v>
       </c>
       <c r="D118">
-        <v>-1.295834564331559</v>
+        <v>-2.381066020335707</v>
       </c>
       <c r="E118">
-        <v>0.1951913018382836</v>
+        <v>0.01736151854810641</v>
       </c>
     </row>
     <row r="119">
@@ -2611,16 +2611,16 @@
         </is>
       </c>
       <c r="B119">
-        <v>-28.69408783308077</v>
+        <v>-250.5849211716044</v>
       </c>
       <c r="C119">
-        <v>28.32046230008675</v>
+        <v>110.2076827790723</v>
       </c>
       <c r="D119">
-        <v>-1.013192776623314</v>
+        <v>-2.273751837010666</v>
       </c>
       <c r="E119">
-        <v>0.3110982593259208</v>
+        <v>0.02309304190594736</v>
       </c>
     </row>
     <row r="120">
@@ -2630,16 +2630,16 @@
         </is>
       </c>
       <c r="B120">
-        <v>-42.19174274624866</v>
+        <v>-285.5297008832448</v>
       </c>
       <c r="C120">
-        <v>28.32046230008806</v>
+        <v>110.2076827790774</v>
       </c>
       <c r="D120">
-        <v>-1.489797104975842</v>
+        <v>-2.590832995333169</v>
       </c>
       <c r="E120">
-        <v>0.1364450638263396</v>
+        <v>0.009648315216971143</v>
       </c>
     </row>
     <row r="121">
@@ -2649,16 +2649,16 @@
         </is>
       </c>
       <c r="B121">
-        <v>-13.8461057005355</v>
+        <v>-220.628042652632</v>
       </c>
       <c r="C121">
-        <v>28.32046230008702</v>
+        <v>110.2076827790734</v>
       </c>
       <c r="D121">
-        <v>-0.488908180728849</v>
+        <v>-2.001929784649511</v>
       </c>
       <c r="E121">
-        <v>0.6249636412923155</v>
+        <v>0.04543549045401953</v>
       </c>
     </row>
     <row r="122">
@@ -2668,16 +2668,16 @@
         </is>
       </c>
       <c r="B122">
-        <v>-37.75489351325889</v>
+        <v>-285.965888281237</v>
       </c>
       <c r="C122">
-        <v>28.32702233870783</v>
+        <v>110.2332108459418</v>
       </c>
       <c r="D122">
-        <v>-1.332822527614144</v>
+        <v>-2.594189954975487</v>
       </c>
       <c r="E122">
-        <v>0.1827512950234989</v>
+        <v>0.009554950506245092</v>
       </c>
     </row>
     <row r="123">
@@ -2687,16 +2687,16 @@
         </is>
       </c>
       <c r="B123">
-        <v>-25.31434545022994</v>
+        <v>-244.7481166453881</v>
       </c>
       <c r="C123">
-        <v>28.32702233870557</v>
+        <v>110.233210845933</v>
       </c>
       <c r="D123">
-        <v>-0.8936465381905262</v>
+        <v>-2.220275675245088</v>
       </c>
       <c r="E123">
-        <v>0.3716252373587451</v>
+        <v>0.02651871098214745</v>
       </c>
     </row>
     <row r="124">
@@ -2706,16 +2706,16 @@
         </is>
       </c>
       <c r="B124">
-        <v>25.76027522239055</v>
+        <v>211.0798910476216</v>
       </c>
       <c r="C124">
-        <v>28.32702233870717</v>
+        <v>110.2332108459392</v>
       </c>
       <c r="D124">
-        <v>0.9093887424655532</v>
+        <v>1.914848432952068</v>
       </c>
       <c r="E124">
-        <v>0.3632613433018332</v>
+        <v>0.05566320365511364</v>
       </c>
     </row>
     <row r="125">
@@ -2725,16 +2725,16 @@
         </is>
       </c>
       <c r="B125">
-        <v>-35.05519577900206</v>
+        <v>-270.7406683994339</v>
       </c>
       <c r="C125">
-        <v>28.32702233870561</v>
+        <v>110.2332108459332</v>
       </c>
       <c r="D125">
-        <v>-1.237517849911925</v>
+        <v>-2.456071689482338</v>
       </c>
       <c r="E125">
-        <v>0.2160491819682602</v>
+        <v>0.01413625168499554</v>
       </c>
     </row>
     <row r="126">
@@ -2744,16 +2744,16 @@
         </is>
       </c>
       <c r="B126">
-        <v>208.3134284798621</v>
+        <v>441.9902231608818</v>
       </c>
       <c r="C126">
-        <v>28.42524124579201</v>
+        <v>110.6154248804495</v>
       </c>
       <c r="D126">
-        <v>7.328466508994017</v>
+        <v>3.99573769787147</v>
       </c>
       <c r="E126">
-        <v>3.437625094196863E-13</v>
+        <v>6.697679314008965E-05</v>
       </c>
     </row>
     <row r="127">
@@ -2763,16 +2763,16 @@
         </is>
       </c>
       <c r="B127">
-        <v>-39.44942682564233</v>
+        <v>-294.0228550838888</v>
       </c>
       <c r="C127">
-        <v>28.32702233870583</v>
+        <v>110.233210845934</v>
       </c>
       <c r="D127">
-        <v>-1.392642910149399</v>
+        <v>-2.667280149308415</v>
       </c>
       <c r="E127">
-        <v>0.1638922121166443</v>
+        <v>0.007712298607813991</v>
       </c>
     </row>
     <row r="128">
@@ -2782,16 +2782,16 @@
         </is>
       </c>
       <c r="B128">
-        <v>-28.28014018382919</v>
+        <v>-221.5814936157882</v>
       </c>
       <c r="C128">
-        <v>28.32702233870517</v>
+        <v>110.2332108459314</v>
       </c>
       <c r="D128">
-        <v>-0.9983449670665905</v>
+        <v>-2.010115571481301</v>
       </c>
       <c r="E128">
-        <v>0.3182403825961683</v>
+        <v>0.04456133787018627</v>
       </c>
     </row>
     <row r="129">
@@ -2801,16 +2801,16 @@
         </is>
       </c>
       <c r="B129">
-        <v>-47.87030438595934</v>
+        <v>-317.6235362901134</v>
       </c>
       <c r="C129">
-        <v>28.32702233870694</v>
+        <v>110.2332108459383</v>
       </c>
       <c r="D129">
-        <v>-1.689916568482662</v>
+        <v>-2.881377888321001</v>
       </c>
       <c r="E129">
-        <v>0.0912094437529954</v>
+        <v>0.004004241414132673</v>
       </c>
     </row>
     <row r="130">
@@ -2820,16 +2820,16 @@
         </is>
       </c>
       <c r="B130">
-        <v>-34.13628100718625</v>
+        <v>-222.589504556287</v>
       </c>
       <c r="C130">
-        <v>28.32702233870514</v>
+        <v>110.2332108459313</v>
       </c>
       <c r="D130">
-        <v>-1.205078338239015</v>
+        <v>-2.019259920382722</v>
       </c>
       <c r="E130">
-        <v>0.228324486137666</v>
+        <v>0.04360165574647674</v>
       </c>
     </row>
     <row r="131">
@@ -2839,16 +2839,16 @@
         </is>
       </c>
       <c r="B131">
-        <v>-45.72027841119363</v>
+        <v>-332.5300814085347</v>
       </c>
       <c r="C131">
-        <v>28.32046230008718</v>
+        <v>110.207682779074</v>
       </c>
       <c r="D131">
-        <v>-1.614390257006959</v>
+        <v>-3.017303993906991</v>
       </c>
       <c r="E131">
-        <v>0.1066103464336991</v>
+        <v>0.002584518513425412</v>
       </c>
     </row>
     <row r="132">
@@ -2858,16 +2858,16 @@
         </is>
       </c>
       <c r="B132">
-        <v>-41.57530502388458</v>
+        <v>-308.938327562303</v>
       </c>
       <c r="C132">
-        <v>28.32702233870651</v>
+        <v>110.2332108459366</v>
       </c>
       <c r="D132">
-        <v>-1.467690621582749</v>
+        <v>-2.802588486641101</v>
       </c>
       <c r="E132">
-        <v>0.1423552853637912</v>
+        <v>0.005121338362261223</v>
       </c>
     </row>
     <row r="133">
@@ -2877,16 +2877,16 @@
         </is>
       </c>
       <c r="B133">
-        <v>-21.40323074062324</v>
+        <v>-255.9603667755754</v>
       </c>
       <c r="C133">
-        <v>28.32046230008664</v>
+        <v>110.2076827790719</v>
       </c>
       <c r="D133">
-        <v>-0.7557514603339563</v>
+        <v>-2.322527434758672</v>
       </c>
       <c r="E133">
-        <v>0.449892751367353</v>
+        <v>0.02031067531088444</v>
       </c>
     </row>
     <row r="134">
@@ -2896,16 +2896,16 @@
         </is>
       </c>
       <c r="B134">
-        <v>-17.40997850703829</v>
+        <v>-165.1539264808962</v>
       </c>
       <c r="C134">
-        <v>28.3270223387072</v>
+        <v>110.2332108459393</v>
       </c>
       <c r="D134">
-        <v>-0.614606727769215</v>
+        <v>-1.498222951263875</v>
       </c>
       <c r="E134">
-        <v>0.5388887259125765</v>
+        <v>0.134242947059929</v>
       </c>
     </row>
     <row r="135">
@@ -2915,16 +2915,16 @@
         </is>
       </c>
       <c r="B135">
-        <v>31.82333344482223</v>
+        <v>7.710886070044391</v>
       </c>
       <c r="C135">
-        <v>28.42524124579248</v>
+        <v>110.6154248804514</v>
       </c>
       <c r="D135">
-        <v>1.119544885112725</v>
+        <v>0.06970895856864449</v>
       </c>
       <c r="E135">
-        <v>0.263050536375004</v>
+        <v>0.9444327130599949</v>
       </c>
     </row>
     <row r="136">
@@ -2934,16 +2934,16 @@
         </is>
       </c>
       <c r="B136">
-        <v>550.2867644738994</v>
+        <v>2245.53608577889</v>
       </c>
       <c r="C136">
-        <v>28.32702233870775</v>
+        <v>110.2332108459415</v>
       </c>
       <c r="D136">
-        <v>19.42621281877391</v>
+        <v>20.37077636173714</v>
       </c>
       <c r="E136">
-        <v>9.165602432145234E-77</v>
+        <v>1.589316734105609E-83</v>
       </c>
     </row>
     <row r="137">
@@ -2953,16 +2953,16 @@
         </is>
       </c>
       <c r="B137">
-        <v>1180.588625575795</v>
+        <v>7294.007810350856</v>
       </c>
       <c r="C137">
-        <v>28.32702233870777</v>
+        <v>110.2332108459416</v>
       </c>
       <c r="D137">
-        <v>41.67711704602876</v>
+        <v>66.16887736804411</v>
       </c>
       <c r="E137">
-        <v>1.489855113024667E-269</v>
+        <v>0</v>
       </c>
     </row>
     <row r="138">
@@ -2972,16 +2972,16 @@
         </is>
       </c>
       <c r="B138">
-        <v>549.8748338119317</v>
+        <v>1907.093985286644</v>
       </c>
       <c r="C138">
-        <v>28.32702233870615</v>
+        <v>110.2332108459352</v>
       </c>
       <c r="D138">
-        <v>19.41167085043671</v>
+        <v>17.30053919913525</v>
       </c>
       <c r="E138">
-        <v>1.160400997365543E-76</v>
+        <v>2.37911421693438E-62</v>
       </c>
     </row>
     <row r="139">
@@ -2991,16 +2991,16 @@
         </is>
       </c>
       <c r="B139">
-        <v>-27.30788181664174</v>
+        <v>-252.9714571850272</v>
       </c>
       <c r="C139">
-        <v>28.32702233870742</v>
+        <v>110.2332108459402</v>
       </c>
       <c r="D139">
-        <v>-0.964022320811564</v>
+        <v>-2.294875158254941</v>
       </c>
       <c r="E139">
-        <v>0.3351585196827472</v>
+        <v>0.02184981251502903</v>
       </c>
     </row>
     <row r="140">
@@ -3010,16 +3010,16 @@
         </is>
       </c>
       <c r="B140">
-        <v>10.26249662472105</v>
+        <v>-144.3390873363311</v>
       </c>
       <c r="C140">
-        <v>28.32702233870669</v>
+        <v>110.2332108459373</v>
       </c>
       <c r="D140">
-        <v>0.362286459268899</v>
+        <v>-1.309397469498194</v>
       </c>
       <c r="E140">
-        <v>0.7171786302849587</v>
+        <v>0.190559494434999</v>
       </c>
     </row>
     <row r="141">
@@ -3029,16 +3029,16 @@
         </is>
       </c>
       <c r="B141">
-        <v>-6.184195816814258</v>
+        <v>-203.927988691859</v>
       </c>
       <c r="C141">
-        <v>28.32702233870588</v>
+        <v>110.2332108459342</v>
       </c>
       <c r="D141">
-        <v>-0.2183143622675867</v>
+        <v>-1.849968690260469</v>
       </c>
       <c r="E141">
-        <v>0.8272078415334883</v>
+        <v>0.06447463963003039</v>
       </c>
     </row>
     <row r="142">
@@ -3048,16 +3048,16 @@
         </is>
       </c>
       <c r="B142">
-        <v>-14.58302015166591</v>
+        <v>-166.2194868354859</v>
       </c>
       <c r="C142">
-        <v>28.42524124579291</v>
+        <v>110.615424880453</v>
       </c>
       <c r="D142">
-        <v>-0.5130306555911562</v>
+        <v>-1.502679097559193</v>
       </c>
       <c r="E142">
-        <v>0.6079900575065675</v>
+        <v>0.1330894946245865</v>
       </c>
     </row>
     <row r="143">
@@ -3067,16 +3067,16 @@
         </is>
       </c>
       <c r="B143">
-        <v>33.25692197299123</v>
+        <v>141.9588170859979</v>
       </c>
       <c r="C143">
-        <v>28.42524124579172</v>
+        <v>110.6154248804484</v>
       </c>
       <c r="D143">
-        <v>1.169978530188018</v>
+        <v>1.283354624722773</v>
       </c>
       <c r="E143">
-        <v>0.2421576701870674</v>
+        <v>0.1995257798305643</v>
       </c>
     </row>
     <row r="144">
@@ -3086,16 +3086,16 @@
         </is>
       </c>
       <c r="B144">
-        <v>5.746001745242373</v>
+        <v>-99.12839806918377</v>
       </c>
       <c r="C144">
-        <v>28.42524124579183</v>
+        <v>110.6154248804488</v>
       </c>
       <c r="D144">
-        <v>0.202144344020054</v>
+        <v>-0.8961534810928943</v>
       </c>
       <c r="E144">
-        <v>0.839825718287162</v>
+        <v>0.3702853448697576</v>
       </c>
     </row>
     <row r="145">
@@ -3105,16 +3105,16 @@
         </is>
       </c>
       <c r="B145">
-        <v>-27.71448484129886</v>
+        <v>-197.1461324037683</v>
       </c>
       <c r="C145">
-        <v>28.425241245793</v>
+        <v>110.6154248804534</v>
       </c>
       <c r="D145">
-        <v>-0.9749955893655139</v>
+        <v>-1.782266194943718</v>
       </c>
       <c r="E145">
-        <v>0.3296876822717565</v>
+        <v>0.07486692126587638</v>
       </c>
     </row>
     <row r="146">
@@ -3124,16 +3124,16 @@
         </is>
       </c>
       <c r="B146">
-        <v>-41.83902858935198</v>
+        <v>-273.1942017308451</v>
       </c>
       <c r="C146">
-        <v>28.32702233870856</v>
+        <v>110.2332108459446</v>
       </c>
       <c r="D146">
-        <v>-1.477000585839176</v>
+        <v>-2.478329349515593</v>
       </c>
       <c r="E146">
-        <v>0.1398426988392553</v>
+        <v>0.01328698118495133</v>
       </c>
     </row>
     <row r="147">
@@ -3143,16 +3143,16 @@
         </is>
       </c>
       <c r="B147">
-        <v>-42.32960335200608</v>
+        <v>-286.8410720960022</v>
       </c>
       <c r="C147">
-        <v>28.42524124579315</v>
+        <v>110.6154248804539</v>
       </c>
       <c r="D147">
-        <v>-1.489155465242383</v>
+        <v>-2.593138094492713</v>
       </c>
       <c r="E147">
-        <v>0.1366138946697775</v>
+        <v>0.009584118039452588</v>
       </c>
     </row>
     <row r="148">
@@ -3162,16 +3162,16 @@
         </is>
       </c>
       <c r="B148">
-        <v>-35.09642510654794</v>
+        <v>-266.6990331536372</v>
       </c>
       <c r="C148">
-        <v>28.32702233870639</v>
+        <v>110.2332108459362</v>
       </c>
       <c r="D148">
-        <v>-1.238973326843173</v>
+        <v>-2.419407283040865</v>
       </c>
       <c r="E148">
-        <v>0.2155097893337942</v>
+        <v>0.01564002007766359</v>
       </c>
     </row>
     <row r="149">
@@ -3181,16 +3181,16 @@
         </is>
       </c>
       <c r="B149">
-        <v>-45.71670046951091</v>
+        <v>-320.2118855662827</v>
       </c>
       <c r="C149">
-        <v>28.32702233870725</v>
+        <v>110.2332108459395</v>
       </c>
       <c r="D149">
-        <v>-1.61389008427623</v>
+        <v>-2.904858554957694</v>
       </c>
       <c r="E149">
-        <v>0.1067188208374424</v>
+        <v>0.003717044942792143</v>
       </c>
     </row>
     <row r="150">
@@ -3200,16 +3200,16 @@
         </is>
       </c>
       <c r="B150">
-        <v>-40.68011343783578</v>
+        <v>-297.6434273881663</v>
       </c>
       <c r="C150">
-        <v>28.32702233870732</v>
+        <v>110.2332108459398</v>
       </c>
       <c r="D150">
-        <v>-1.43608858535931</v>
+        <v>-2.700124809066372</v>
       </c>
       <c r="E150">
-        <v>0.1511432395096031</v>
+        <v>0.006993394056290862</v>
       </c>
     </row>
     <row r="151">
@@ -3219,16 +3219,16 @@
         </is>
       </c>
       <c r="B151">
-        <v>-43.29516365501004</v>
+        <v>-303.91735211822</v>
       </c>
       <c r="C151">
-        <v>28.32046230008617</v>
+        <v>110.2076827790701</v>
       </c>
       <c r="D151">
-        <v>-1.528759071665236</v>
+        <v>-2.757678452667168</v>
       </c>
       <c r="E151">
-        <v>0.1264921401266849</v>
+        <v>0.00587756775253337</v>
       </c>
     </row>
     <row r="152">
@@ -3238,16 +3238,16 @@
         </is>
       </c>
       <c r="B152">
-        <v>-11.11491942387592</v>
+        <v>-201.4743955773955</v>
       </c>
       <c r="C152">
-        <v>28.32046230008812</v>
+        <v>110.2076827790777</v>
       </c>
       <c r="D152">
-        <v>-0.3924695616229871</v>
+        <v>-1.828133851441837</v>
       </c>
       <c r="E152">
-        <v>0.6947557167646308</v>
+        <v>0.06768760641930842</v>
       </c>
     </row>
     <row r="153">
@@ -3257,16 +3257,16 @@
         </is>
       </c>
       <c r="B153">
-        <v>-39.98761209479787</v>
+        <v>-281.6561267567295</v>
       </c>
       <c r="C153">
-        <v>28.32702233870782</v>
+        <v>110.2332108459417</v>
       </c>
       <c r="D153">
-        <v>-1.41164191621215</v>
+        <v>-2.555093193741429</v>
       </c>
       <c r="E153">
-        <v>0.158220639418353</v>
+        <v>0.01069394471490107</v>
       </c>
     </row>
     <row r="154">
@@ -3276,16 +3276,16 @@
         </is>
       </c>
       <c r="B154">
-        <v>-40.47129773971761</v>
+        <v>-297.0830298009799</v>
       </c>
       <c r="C154">
-        <v>28.3270223387068</v>
+        <v>110.2332108459378</v>
       </c>
       <c r="D154">
-        <v>-1.428716977584211</v>
+        <v>-2.695041063588214</v>
       </c>
       <c r="E154">
-        <v>0.1532514494713197</v>
+        <v>0.00710057229688986</v>
       </c>
     </row>
     <row r="155">
@@ -3295,16 +3295,16 @@
         </is>
       </c>
       <c r="B155">
-        <v>-49.797657721595</v>
+        <v>-324.3220599477302</v>
       </c>
       <c r="C155">
-        <v>28.42524124579318</v>
+        <v>110.6154248804541</v>
       </c>
       <c r="D155">
-        <v>-1.751881621372865</v>
+        <v>-2.931978612370167</v>
       </c>
       <c r="E155">
-        <v>0.07995694244477547</v>
+        <v>0.003408738062274468</v>
       </c>
     </row>
     <row r="156">
@@ -3314,16 +3314,16 @@
         </is>
       </c>
       <c r="B156">
-        <v>14.70656033164034</v>
+        <v>-159.2809025705883</v>
       </c>
       <c r="C156">
-        <v>28.32702233870601</v>
+        <v>110.2332108459347</v>
       </c>
       <c r="D156">
-        <v>0.5191707111250204</v>
+        <v>-1.444944779783329</v>
       </c>
       <c r="E156">
-        <v>0.6037027142511144</v>
+        <v>0.1486397815532857</v>
       </c>
     </row>
     <row r="157">
@@ -3333,16 +3333,16 @@
         </is>
       </c>
       <c r="B157">
-        <v>-37.34308066230935</v>
+        <v>-267.1202098728073</v>
       </c>
       <c r="C157">
-        <v>28.3270223387064</v>
+        <v>110.2332108459362</v>
       </c>
       <c r="D157">
-        <v>-1.31828471823822</v>
+        <v>-2.423228061878184</v>
       </c>
       <c r="E157">
-        <v>0.1875686857891654</v>
+        <v>0.01547699591224059</v>
       </c>
     </row>
     <row r="158">
@@ -3352,16 +3352,16 @@
         </is>
       </c>
       <c r="B158">
-        <v>-37.29668630101673</v>
+        <v>-298.9932347989374</v>
       </c>
       <c r="C158">
-        <v>28.32702233870791</v>
+        <v>110.2332108459421</v>
       </c>
       <c r="D158">
-        <v>-1.316646905384478</v>
+        <v>-2.712369824886979</v>
       </c>
       <c r="E158">
-        <v>0.1881172333292065</v>
+        <v>0.006741183545401402</v>
       </c>
     </row>
     <row r="159">
@@ -3371,16 +3371,16 @@
         </is>
       </c>
       <c r="B159">
-        <v>84.90777971375392</v>
+        <v>622.6679154037239</v>
       </c>
       <c r="C159">
-        <v>28.42524124579374</v>
+        <v>110.6154248804562</v>
       </c>
       <c r="D159">
-        <v>2.987055729080867</v>
+        <v>5.629123750839004</v>
       </c>
       <c r="E159">
-        <v>0.002853164542519934</v>
+        <v>2.083603408658626E-08</v>
       </c>
     </row>
     <row r="160">
@@ -3390,16 +3390,16 @@
         </is>
       </c>
       <c r="B160">
-        <v>-22.21963996450337</v>
+        <v>-190.7185967741432</v>
       </c>
       <c r="C160">
-        <v>28.32046230008823</v>
+        <v>110.2076827790781</v>
       </c>
       <c r="D160">
-        <v>-0.784578999066486</v>
+        <v>-1.730538125517592</v>
       </c>
       <c r="E160">
-        <v>0.432799137496244</v>
+        <v>0.08369800698922157</v>
       </c>
     </row>
     <row r="161">
@@ -3409,16 +3409,16 @@
         </is>
       </c>
       <c r="B161">
-        <v>-36.13832931403035</v>
+        <v>-290.3436166199189</v>
       </c>
       <c r="C161">
-        <v>28.32702233870719</v>
+        <v>110.2332108459393</v>
       </c>
       <c r="D161">
-        <v>-1.27575460921812</v>
+        <v>-2.63390328914305</v>
       </c>
       <c r="E161">
-        <v>0.2021996283496151</v>
+        <v>0.008510075396046646</v>
       </c>
     </row>
     <row r="162">
@@ -3428,16 +3428,16 @@
         </is>
       </c>
       <c r="B162">
-        <v>-46.88180524770248</v>
+        <v>-320.1936672853369</v>
       </c>
       <c r="C162">
-        <v>28.32046230008791</v>
+        <v>110.2076827790768</v>
       </c>
       <c r="D162">
-        <v>-1.655403953188891</v>
+        <v>-2.905366116146364</v>
       </c>
       <c r="E162">
-        <v>0.09800921952245599</v>
+        <v>0.003711049216347881</v>
       </c>
     </row>
     <row r="163">
@@ -3447,16 +3447,16 @@
         </is>
       </c>
       <c r="B163">
-        <v>-41.57909602138297</v>
+        <v>-306.1590322198155</v>
       </c>
       <c r="C163">
-        <v>28.32046230008682</v>
+        <v>110.2076827790726</v>
       </c>
       <c r="D163">
-        <v>-1.468164452289167</v>
+        <v>-2.778018959291214</v>
       </c>
       <c r="E163">
-        <v>0.1422265750165254</v>
+        <v>0.005523387025746573</v>
       </c>
     </row>
     <row r="164">
@@ -3466,16 +3466,16 @@
         </is>
       </c>
       <c r="B164">
-        <v>-36.02843904293017</v>
+        <v>-289.3389408857107</v>
       </c>
       <c r="C164">
-        <v>28.32046230008687</v>
+        <v>110.2076827790728</v>
       </c>
       <c r="D164">
-        <v>-1.272169877072228</v>
+        <v>-2.625397191824933</v>
       </c>
       <c r="E164">
-        <v>0.2034698467028796</v>
+        <v>0.008724852823784213</v>
       </c>
     </row>
     <row r="165">
@@ -3485,16 +3485,16 @@
         </is>
       </c>
       <c r="B165">
-        <v>142.4418993086508</v>
+        <v>34.05441877059023</v>
       </c>
       <c r="C165">
-        <v>28.32046230008751</v>
+        <v>110.2076827790753</v>
       </c>
       <c r="D165">
-        <v>5.029645978208862</v>
+        <v>0.3090022211868519</v>
       </c>
       <c r="E165">
-        <v>5.380836710341019E-07</v>
+        <v>0.7573540219051741</v>
       </c>
     </row>
     <row r="166">
@@ -3504,16 +3504,16 @@
         </is>
       </c>
       <c r="B166">
-        <v>69.25279403200985</v>
+        <v>-28.3478659285312</v>
       </c>
       <c r="C166">
-        <v>28.32702233870827</v>
+        <v>110.2332108459435</v>
       </c>
       <c r="D166">
-        <v>2.444760808388158</v>
+        <v>-0.2571626618782681</v>
       </c>
       <c r="E166">
-        <v>0.01458593240927184</v>
+        <v>0.7970813032720273</v>
       </c>
     </row>
     <row r="167">
@@ -3523,16 +3523,16 @@
         </is>
       </c>
       <c r="B167">
-        <v>30.49719173634987</v>
+        <v>-199.1415362005258</v>
       </c>
       <c r="C167">
-        <v>28.32702233870662</v>
+        <v>110.2332108459371</v>
       </c>
       <c r="D167">
-        <v>1.076611278506244</v>
+        <v>-1.806547542907444</v>
       </c>
       <c r="E167">
-        <v>0.2817918766640617</v>
+        <v>0.07099244119701215</v>
       </c>
     </row>
     <row r="168">
@@ -3542,16 +3542,16 @@
         </is>
       </c>
       <c r="B168">
-        <v>107.3168422564071</v>
+        <v>171.8721995304434</v>
       </c>
       <c r="C168">
-        <v>28.32702233870577</v>
+        <v>110.2332108459338</v>
       </c>
       <c r="D168">
-        <v>3.788497109693397</v>
+        <v>1.559168949280256</v>
       </c>
       <c r="E168">
-        <v>0.0001563215426275559</v>
+        <v>0.1191244409116749</v>
       </c>
     </row>
     <row r="169">
@@ -3561,16 +3561,16 @@
         </is>
       </c>
       <c r="B169">
-        <v>18.43263788431372</v>
+        <v>-95.49558997425353</v>
       </c>
       <c r="C169">
-        <v>28.32702233870682</v>
+        <v>110.2332108459378</v>
       </c>
       <c r="D169">
-        <v>0.6507086295168714</v>
+        <v>-0.8663050748627685</v>
       </c>
       <c r="E169">
-        <v>0.5153139811462043</v>
+        <v>0.3864332515850336</v>
       </c>
     </row>
     <row r="170">
@@ -3580,16 +3580,16 @@
         </is>
       </c>
       <c r="B170">
-        <v>-17.05282621430701</v>
+        <v>-258.745201178355</v>
       </c>
       <c r="C170">
-        <v>28.32702233870751</v>
+        <v>110.2332108459405</v>
       </c>
       <c r="D170">
-        <v>-0.6019985443724225</v>
+        <v>-2.347252694471283</v>
       </c>
       <c r="E170">
-        <v>0.5472475827067473</v>
+        <v>0.01901549326536228</v>
       </c>
     </row>
     <row r="171">
@@ -3599,16 +3599,16 @@
         </is>
       </c>
       <c r="B171">
-        <v>98.01833655750124</v>
+        <v>-56.44067738730992</v>
       </c>
       <c r="C171">
-        <v>28.3204623000879</v>
+        <v>110.2076827790768</v>
       </c>
       <c r="D171">
-        <v>3.461042956110114</v>
+        <v>-0.5121301524908328</v>
       </c>
       <c r="E171">
-        <v>0.0005500909516322933</v>
+        <v>0.6086199817294031</v>
       </c>
     </row>
     <row r="172">
@@ -3618,16 +3618,16 @@
         </is>
       </c>
       <c r="B172">
-        <v>-18.96411891389016</v>
+        <v>-288.6141857395418</v>
       </c>
       <c r="C172">
-        <v>28.32702233870599</v>
+        <v>110.2332108459347</v>
       </c>
       <c r="D172">
-        <v>-0.6694709626425374</v>
+        <v>-2.618214452112058</v>
       </c>
       <c r="E172">
-        <v>0.5032771746820881</v>
+        <v>0.008909977183123348</v>
       </c>
     </row>
     <row r="173">
@@ -3637,16 +3637,16 @@
         </is>
       </c>
       <c r="B173">
-        <v>-31.26998415149754</v>
+        <v>-303.7682248343253</v>
       </c>
       <c r="C173">
-        <v>28.32702233870664</v>
+        <v>110.2332108459371</v>
       </c>
       <c r="D173">
-        <v>-1.103892381543032</v>
+        <v>-2.755686988550795</v>
       </c>
       <c r="E173">
-        <v>0.2697808696193009</v>
+        <v>0.005913322582429291</v>
       </c>
     </row>
     <row r="174">
@@ -3656,16 +3656,16 @@
         </is>
       </c>
       <c r="B174">
-        <v>-46.7508181698461</v>
+        <v>-337.5917406809546</v>
       </c>
       <c r="C174">
-        <v>28.42524124579278</v>
+        <v>110.6154248804525</v>
       </c>
       <c r="D174">
-        <v>-1.644693804551815</v>
+        <v>-3.051940911909949</v>
       </c>
       <c r="E174">
-        <v>0.1001998864292528</v>
+        <v>0.002305445098941819</v>
       </c>
     </row>
     <row r="175">
@@ -3675,16 +3675,16 @@
         </is>
       </c>
       <c r="B175">
-        <v>33.35225916318349</v>
+        <v>3.824348436707376</v>
       </c>
       <c r="C175">
-        <v>28.32702233870753</v>
+        <v>110.2332108459406</v>
       </c>
       <c r="D175">
-        <v>1.177400814119782</v>
+        <v>0.03469325085751333</v>
       </c>
       <c r="E175">
-        <v>0.2391843595855211</v>
+        <v>0.9723280198373435</v>
       </c>
     </row>
     <row r="176">
@@ -3694,16 +3694,16 @@
         </is>
       </c>
       <c r="B176">
-        <v>3.962514032961482</v>
+        <v>-146.428713002661</v>
       </c>
       <c r="C176">
-        <v>28.3270223387072</v>
+        <v>110.2332108459393</v>
       </c>
       <c r="D176">
-        <v>0.1398845944900795</v>
+        <v>-1.328353877011784</v>
       </c>
       <c r="E176">
-        <v>0.8887661336194934</v>
+        <v>0.1842221980713926</v>
       </c>
     </row>
     <row r="177">
@@ -3713,16 +3713,16 @@
         </is>
       </c>
       <c r="B177">
-        <v>-11.87636266041351</v>
+        <v>-162.9512599034343</v>
       </c>
       <c r="C177">
-        <v>28.32702233870623</v>
+        <v>110.2332108459356</v>
       </c>
       <c r="D177">
-        <v>-0.419259127147493</v>
+        <v>-1.478241073202328</v>
       </c>
       <c r="E177">
-        <v>0.6750745870110487</v>
+        <v>0.1395105088989311</v>
       </c>
     </row>
     <row r="178">
@@ -3732,16 +3732,16 @@
         </is>
       </c>
       <c r="B178">
-        <v>-20.72110101446636</v>
+        <v>-269.2187757185462</v>
       </c>
       <c r="C178">
-        <v>28.32702233870707</v>
+        <v>110.2332108459388</v>
       </c>
       <c r="D178">
-        <v>-0.7314959111022514</v>
+        <v>-2.442265571804893</v>
       </c>
       <c r="E178">
-        <v>0.4645673211259352</v>
+        <v>0.01468681706635632</v>
       </c>
     </row>
     <row r="179">
@@ -3751,16 +3751,16 @@
         </is>
       </c>
       <c r="B179">
-        <v>3.27337277380244</v>
+        <v>-190.9503267512668</v>
       </c>
       <c r="C179">
-        <v>28.32046230008681</v>
+        <v>110.2076827790725</v>
       </c>
       <c r="D179">
-        <v>0.1155833100151196</v>
+        <v>-1.732640791786311</v>
       </c>
       <c r="E179">
-        <v>0.9079951151083274</v>
+        <v>0.08332326659218396</v>
       </c>
     </row>
     <row r="180">
@@ -3770,16 +3770,16 @@
         </is>
       </c>
       <c r="B180">
-        <v>-23.99162964891988</v>
+        <v>-216.9640582626532</v>
       </c>
       <c r="C180">
-        <v>28.32702233870634</v>
+        <v>110.233210845936</v>
       </c>
       <c r="D180">
-        <v>-0.8469520503091306</v>
+        <v>-1.968227692885461</v>
       </c>
       <c r="E180">
-        <v>0.3971294764964539</v>
+        <v>0.04918835447229738</v>
       </c>
     </row>
     <row r="181">
@@ -3789,16 +3789,16 @@
         </is>
       </c>
       <c r="B181">
-        <v>-41.90879783876898</v>
+        <v>-304.4929506237864</v>
       </c>
       <c r="C181">
-        <v>28.32702233870711</v>
+        <v>110.233210845939</v>
       </c>
       <c r="D181">
-        <v>-1.479463578545748</v>
+        <v>-2.762261466277555</v>
       </c>
       <c r="E181">
-        <v>0.139183729412382</v>
+        <v>0.005796023885660515</v>
       </c>
     </row>
     <row r="182">
@@ -3808,16 +3808,16 @@
         </is>
       </c>
       <c r="B182">
-        <v>115.4170036301652</v>
+        <v>443.0839822744219</v>
       </c>
       <c r="C182">
-        <v>28.32702233870594</v>
+        <v>110.2332108459344</v>
       </c>
       <c r="D182">
-        <v>4.074448851352083</v>
+        <v>4.01951443556961</v>
       </c>
       <c r="E182">
-        <v>4.803828285524142E-05</v>
+        <v>6.06159373393905E-05</v>
       </c>
     </row>
     <row r="183">
@@ -3827,16 +3827,16 @@
         </is>
       </c>
       <c r="B183">
-        <v>3.466413238092634</v>
+        <v>-160.5452394579769</v>
       </c>
       <c r="C183">
-        <v>28.32702233870599</v>
+        <v>110.2332108459346</v>
       </c>
       <c r="D183">
-        <v>0.1223712537323817</v>
+        <v>-1.456414434687564</v>
       </c>
       <c r="E183">
-        <v>0.9026180617901417</v>
+        <v>0.1454448036146416</v>
       </c>
     </row>
     <row r="184">
@@ -3846,16 +3846,16 @@
         </is>
       </c>
       <c r="B184">
-        <v>-21.56662811203665</v>
+        <v>-271.3427939830231</v>
       </c>
       <c r="C184">
-        <v>28.3270223387066</v>
+        <v>110.233210845937</v>
       </c>
       <c r="D184">
-        <v>-0.7613446925047107</v>
+        <v>-2.461533977834089</v>
       </c>
       <c r="E184">
-        <v>0.4465465484494797</v>
+        <v>0.01392350778152381</v>
       </c>
     </row>
     <row r="185">
@@ -3865,16 +3865,16 @@
         </is>
       </c>
       <c r="B185">
-        <v>13.8814990399717</v>
+        <v>-121.5766377615453</v>
       </c>
       <c r="C185">
-        <v>28.32046230008752</v>
+        <v>110.2076827790753</v>
       </c>
       <c r="D185">
-        <v>0.4901579251384185</v>
+        <v>-1.103159368709897</v>
       </c>
       <c r="E185">
-        <v>0.6240792559653231</v>
+        <v>0.2700989257775196</v>
       </c>
     </row>
     <row r="186">
@@ -3884,16 +3884,16 @@
         </is>
       </c>
       <c r="B186">
-        <v>-4.622519874409726</v>
+        <v>-231.3362970292832</v>
       </c>
       <c r="C186">
-        <v>28.32046230008781</v>
+        <v>110.2076827790764</v>
       </c>
       <c r="D186">
-        <v>-0.1632219073766813</v>
+        <v>-2.099094103022042</v>
       </c>
       <c r="E186">
-        <v>0.8703612330086909</v>
+        <v>0.03594144650205523</v>
       </c>
     </row>
     <row r="187">
@@ -3903,16 +3903,16 @@
         </is>
       </c>
       <c r="B187">
-        <v>-30.53010424229413</v>
+        <v>-274.2139558393052</v>
       </c>
       <c r="C187">
-        <v>28.32046230008748</v>
+        <v>110.2076827790752</v>
       </c>
       <c r="D187">
-        <v>-1.078022806223747</v>
+        <v>-2.488156441770042</v>
       </c>
       <c r="E187">
-        <v>0.2811616569866181</v>
+        <v>0.01292660439831776</v>
       </c>
     </row>
     <row r="188">
@@ -3922,16 +3922,16 @@
         </is>
       </c>
       <c r="B188">
-        <v>18.01831914762289</v>
+        <v>-69.78298466238907</v>
       </c>
       <c r="C188">
-        <v>28.32046230008737</v>
+        <v>110.2076827790747</v>
       </c>
       <c r="D188">
-        <v>0.6362296969837001</v>
+        <v>-0.6331952809703648</v>
       </c>
       <c r="E188">
-        <v>0.5247040438703595</v>
+        <v>0.5266830193007415</v>
       </c>
     </row>
     <row r="189">
@@ -3941,16 +3941,16 @@
         </is>
       </c>
       <c r="B189">
-        <v>-6.939129031183807</v>
+        <v>-216.9960688677479</v>
       </c>
       <c r="C189">
-        <v>28.32702233870612</v>
+        <v>110.2332108459351</v>
       </c>
       <c r="D189">
-        <v>-0.2449650001405959</v>
+        <v>-1.968518082731232</v>
       </c>
       <c r="E189">
-        <v>0.8065102237151396</v>
+        <v>0.04915493907243657</v>
       </c>
     </row>
     <row r="190">
@@ -3960,16 +3960,16 @@
         </is>
       </c>
       <c r="B190">
-        <v>-28.27097295431418</v>
+        <v>-286.3792554573703</v>
       </c>
       <c r="C190">
-        <v>28.32046230008704</v>
+        <v>110.2076827790735</v>
       </c>
       <c r="D190">
-        <v>-0.9982525233787336</v>
+        <v>-2.598541664572125</v>
       </c>
       <c r="E190">
-        <v>0.3182851841411722</v>
+        <v>0.00943511993326689</v>
       </c>
     </row>
     <row r="191">
@@ -3979,16 +3979,16 @@
         </is>
       </c>
       <c r="B191">
-        <v>21.426447984229</v>
+        <v>-208.4809382950808</v>
       </c>
       <c r="C191">
-        <v>28.32046230008731</v>
+        <v>110.2076827790745</v>
       </c>
       <c r="D191">
-        <v>0.7565712648752539</v>
+        <v>-1.891709661594171</v>
       </c>
       <c r="E191">
-        <v>0.4494014079016176</v>
+        <v>0.05868299380600881</v>
       </c>
     </row>
     <row r="192">
@@ -3998,16 +3998,16 @@
         </is>
       </c>
       <c r="B192">
-        <v>-26.1337669735887</v>
+        <v>-277.0457475372532</v>
       </c>
       <c r="C192">
-        <v>28.32702233870637</v>
+        <v>110.2332108459361</v>
       </c>
       <c r="D192">
-        <v>-0.9225737411121825</v>
+        <v>-2.51326932610588</v>
       </c>
       <c r="E192">
-        <v>0.3563475785477934</v>
+        <v>0.01204469442404013</v>
       </c>
     </row>
     <row r="193">
@@ -4017,16 +4017,16 @@
         </is>
       </c>
       <c r="B193">
-        <v>16.14897970550225</v>
+        <v>-80.56611728741046</v>
       </c>
       <c r="C193">
-        <v>28.32046230008684</v>
+        <v>110.2076827790727</v>
       </c>
       <c r="D193">
-        <v>0.5702230258244314</v>
+        <v>-0.7310390279134801</v>
       </c>
       <c r="E193">
-        <v>0.5685944701132086</v>
+        <v>0.4648462686165712</v>
       </c>
     </row>
     <row r="194">
@@ -4036,16 +4036,16 @@
         </is>
       </c>
       <c r="B194">
-        <v>-36.27032406206575</v>
+        <v>-307.0278034060794</v>
       </c>
       <c r="C194">
-        <v>28.32046230008709</v>
+        <v>110.2076827790737</v>
       </c>
       <c r="D194">
-        <v>-1.280710875328974</v>
+        <v>-2.785901995794236</v>
       </c>
       <c r="E194">
-        <v>0.200452959816915</v>
+        <v>0.005391388681791064</v>
       </c>
     </row>
     <row r="195">
@@ -4055,16 +4055,16 @@
         </is>
       </c>
       <c r="B195">
-        <v>-31.94345936620276</v>
+        <v>-303.3968179949613</v>
       </c>
       <c r="C195">
-        <v>28.32702233870636</v>
+        <v>110.2332108459361</v>
       </c>
       <c r="D195">
-        <v>-1.127667390672223</v>
+        <v>-2.752317705949745</v>
       </c>
       <c r="E195">
-        <v>0.2596040809136946</v>
+        <v>0.005974261786230836</v>
       </c>
     </row>
     <row r="196">
@@ -4074,16 +4074,16 @@
         </is>
       </c>
       <c r="B196">
-        <v>47.45564610110353</v>
+        <v>-2.80414375413246</v>
       </c>
       <c r="C196">
-        <v>28.32046230008659</v>
+        <v>110.2076827790717</v>
       </c>
       <c r="D196">
-        <v>1.675666364420839</v>
+        <v>-0.02544417669822346</v>
       </c>
       <c r="E196">
-        <v>0.09396958334957534</v>
+        <v>0.9797033706531419</v>
       </c>
     </row>
     <row r="197">
@@ -4093,16 +4093,16 @@
         </is>
       </c>
       <c r="B197">
-        <v>-24.03862962446665</v>
+        <v>-274.7977434693669</v>
       </c>
       <c r="C197">
-        <v>28.32046230008682</v>
+        <v>110.2076827790726</v>
       </c>
       <c r="D197">
-        <v>-0.8488078114598063</v>
+        <v>-2.493453600873172</v>
       </c>
       <c r="E197">
-        <v>0.3960961343719748</v>
+        <v>0.01273596046155902</v>
       </c>
     </row>
     <row r="198">
@@ -4112,16 +4112,16 @@
         </is>
       </c>
       <c r="B198">
-        <v>-17.58200732280925</v>
+        <v>-223.2715927638759</v>
       </c>
       <c r="C198">
-        <v>28.32046230008743</v>
+        <v>110.207682779075</v>
       </c>
       <c r="D198">
-        <v>-0.6208234574883679</v>
+        <v>-2.02591677035304</v>
       </c>
       <c r="E198">
-        <v>0.5347909230819318</v>
+        <v>0.04291407104843802</v>
       </c>
     </row>
     <row r="199">
@@ -4131,16 +4131,16 @@
         </is>
       </c>
       <c r="B199">
-        <v>-31.72982942586593</v>
+        <v>-286.1328478270132</v>
       </c>
       <c r="C199">
-        <v>28.32046230008713</v>
+        <v>110.2076827790738</v>
       </c>
       <c r="D199">
-        <v>-1.120385292077959</v>
+        <v>-2.596305816542801</v>
       </c>
       <c r="E199">
-        <v>0.2626924847844448</v>
+        <v>0.009496518614864006</v>
       </c>
     </row>
     <row r="200">
@@ -4150,16 +4150,16 @@
         </is>
       </c>
       <c r="B200">
-        <v>50.67539457015926</v>
+        <v>-109.5841211362571</v>
       </c>
       <c r="C200">
-        <v>28.32046230008679</v>
+        <v>110.2076827790725</v>
       </c>
       <c r="D200">
-        <v>1.789356191759764</v>
+        <v>-0.9943419403521492</v>
       </c>
       <c r="E200">
-        <v>0.07371813355588509</v>
+        <v>0.3201841805253798</v>
       </c>
     </row>
     <row r="201">
@@ -4169,16 +4169,16 @@
         </is>
       </c>
       <c r="B201">
-        <v>-21.47636238613214</v>
+        <v>-223.7360779999726</v>
       </c>
       <c r="C201">
-        <v>28.32046230008754</v>
+        <v>110.2076827790754</v>
       </c>
       <c r="D201">
-        <v>-0.7583337502956565</v>
+        <v>-2.030131406069744</v>
       </c>
       <c r="E201">
-        <v>0.4483461079615775</v>
+        <v>0.04248350211151668</v>
       </c>
     </row>
     <row r="202">
@@ -4188,16 +4188,16 @@
         </is>
       </c>
       <c r="B202">
-        <v>-36.95965057882169</v>
+        <v>-236.5317030283335</v>
       </c>
       <c r="C202">
-        <v>28.32046230008737</v>
+        <v>110.2076827790747</v>
       </c>
       <c r="D202">
-        <v>-1.305051103586952</v>
+        <v>-2.146236061441299</v>
       </c>
       <c r="E202">
-        <v>0.1920348997732212</v>
+        <v>0.03198159907871068</v>
       </c>
     </row>
     <row r="203">
@@ -4207,16 +4207,16 @@
         </is>
       </c>
       <c r="B203">
-        <v>13.97601283321577</v>
+        <v>-60.96844653201554</v>
       </c>
       <c r="C203">
-        <v>28.32046230008785</v>
+        <v>110.2076827790766</v>
       </c>
       <c r="D203">
-        <v>0.493495222116216</v>
+        <v>-0.5532141225964571</v>
       </c>
       <c r="E203">
-        <v>0.6217202659405767</v>
+        <v>0.5801824705815726</v>
       </c>
     </row>
     <row r="204">
@@ -4226,16 +4226,16 @@
         </is>
       </c>
       <c r="B204">
-        <v>-47.23323730580065</v>
+        <v>-336.713257273644</v>
       </c>
       <c r="C204">
-        <v>28.32046230008773</v>
+        <v>110.2076827790761</v>
       </c>
       <c r="D204">
-        <v>-1.667813074705858</v>
+        <v>-3.055261201241516</v>
       </c>
       <c r="E204">
-        <v>0.09551911164633008</v>
+        <v>0.00228019871618123</v>
       </c>
     </row>
     <row r="205">
@@ -4245,16 +4245,16 @@
         </is>
       </c>
       <c r="B205">
-        <v>-28.66764958036029</v>
+        <v>-252.0415243526307</v>
       </c>
       <c r="C205">
-        <v>28.32046230008692</v>
+        <v>110.207682779073</v>
       </c>
       <c r="D205">
-        <v>-1.012259237741056</v>
+        <v>-2.286968730282478</v>
       </c>
       <c r="E205">
-        <v>0.3115441700922867</v>
+        <v>0.0223081543189542</v>
       </c>
     </row>
     <row r="206">
@@ -4264,16 +4264,16 @@
         </is>
       </c>
       <c r="B206">
-        <v>-39.79143417642391</v>
+        <v>-314.3706887361478</v>
       </c>
       <c r="C206">
-        <v>28.32046230008722</v>
+        <v>110.2076827790741</v>
       </c>
       <c r="D206">
-        <v>-1.405041829995175</v>
+        <v>-2.852529703998453</v>
       </c>
       <c r="E206">
-        <v>0.1601737875734029</v>
+        <v>0.004384625138058965</v>
       </c>
     </row>
     <row r="207">
@@ -4283,16 +4283,16 @@
         </is>
       </c>
       <c r="B207">
-        <v>-40.32473874893662</v>
+        <v>-306.9492261379394</v>
       </c>
       <c r="C207">
-        <v>28.32046230008768</v>
+        <v>110.207682779076</v>
       </c>
       <c r="D207">
-        <v>-1.423872898741903</v>
+        <v>-2.785189003141048</v>
       </c>
       <c r="E207">
-        <v>0.1546489489229659</v>
+        <v>0.005403209126739205</v>
       </c>
     </row>
     <row r="208">
@@ -4302,16 +4302,16 @@
         </is>
       </c>
       <c r="B208">
-        <v>1.732493698690156</v>
+        <v>-193.1387991383967</v>
       </c>
       <c r="C208">
-        <v>28.32046230008732</v>
+        <v>110.2076827790745</v>
       </c>
       <c r="D208">
-        <v>0.06117462632962789</v>
+        <v>-1.752498503444341</v>
       </c>
       <c r="E208">
-        <v>0.9512266291803044</v>
+        <v>0.07985087190907449</v>
       </c>
     </row>
     <row r="209">
@@ -4321,16 +4321,16 @@
         </is>
       </c>
       <c r="B209">
-        <v>-38.57568209441593</v>
+        <v>-309.6996545699782</v>
       </c>
       <c r="C209">
-        <v>28.32046230008781</v>
+        <v>110.2076827790765</v>
       </c>
       <c r="D209">
-        <v>-1.362113431824039</v>
+        <v>-2.810145778954499</v>
       </c>
       <c r="E209">
-        <v>0.1733250046396988</v>
+        <v>0.005003107706980661</v>
       </c>
     </row>
     <row r="210">
@@ -4340,16 +4340,16 @@
         </is>
       </c>
       <c r="B210">
-        <v>-38.25627157475689</v>
+        <v>-305.5874245575596</v>
       </c>
       <c r="C210">
-        <v>28.32046230008741</v>
+        <v>110.2076827790749</v>
       </c>
       <c r="D210">
-        <v>-1.350834995890544</v>
+        <v>-2.772832318506758</v>
       </c>
       <c r="E210">
-        <v>0.1769105931967446</v>
+        <v>0.005611820125685412</v>
       </c>
     </row>
     <row r="211">
@@ -4359,16 +4359,16 @@
         </is>
       </c>
       <c r="B211">
-        <v>1227.822923881923</v>
+        <v>5637.512166691195</v>
       </c>
       <c r="C211">
-        <v>28.32046230008698</v>
+        <v>110.2076827790732</v>
       </c>
       <c r="D211">
-        <v>43.35462150553072</v>
+        <v>51.15353144655423</v>
       </c>
       <c r="E211">
-        <v>2.301394215600398E-285</v>
+        <v>0</v>
       </c>
     </row>
     <row r="212">
@@ -4378,16 +4378,16 @@
         </is>
       </c>
       <c r="B212">
-        <v>517.2186677350405</v>
+        <v>1307.530447892653</v>
       </c>
       <c r="C212">
-        <v>28.3204623000874</v>
+        <v>110.2076827790748</v>
       </c>
       <c r="D212">
-        <v>18.26307290659745</v>
+        <v>11.86424044967684</v>
       </c>
       <c r="E212">
-        <v>9.828456376242893E-69</v>
+        <v>2.307264312817167E-31</v>
       </c>
     </row>
     <row r="213">
@@ -4397,16 +4397,16 @@
         </is>
       </c>
       <c r="B213">
-        <v>-12.42259844016712</v>
+        <v>-131.4201104162144</v>
       </c>
       <c r="C213">
-        <v>28.32702233870667</v>
+        <v>110.2332108459373</v>
       </c>
       <c r="D213">
-        <v>-0.4385423321812617</v>
+        <v>-1.192200693490532</v>
       </c>
       <c r="E213">
-        <v>0.6610434984662127</v>
+        <v>0.2333327832877787</v>
       </c>
     </row>
     <row r="214">
@@ -4416,16 +4416,16 @@
         </is>
       </c>
       <c r="B214">
-        <v>32.23130226243676</v>
+        <v>93.68073196469393</v>
       </c>
       <c r="C214">
-        <v>28.32046230008722</v>
+        <v>110.2076827790742</v>
       </c>
       <c r="D214">
-        <v>1.138092377197441</v>
+        <v>0.8500381244063476</v>
       </c>
       <c r="E214">
-        <v>0.2552266931616108</v>
+        <v>0.3954119567492219</v>
       </c>
     </row>
     <row r="215">
@@ -4435,16 +4435,16 @@
         </is>
       </c>
       <c r="B215">
-        <v>22.25010415916762</v>
+        <v>21.29248293565189</v>
       </c>
       <c r="C215">
-        <v>28.32046230008742</v>
+        <v>110.2076827790749</v>
       </c>
       <c r="D215">
-        <v>0.7856546945951138</v>
+        <v>0.1932032540629253</v>
       </c>
       <c r="E215">
-        <v>0.4321686576754986</v>
+        <v>0.846820626882299</v>
       </c>
     </row>
     <row r="216">
@@ -4454,16 +4454,16 @@
         </is>
       </c>
       <c r="B216">
-        <v>5.126366427582965</v>
+        <v>-65.84879844047803</v>
       </c>
       <c r="C216">
-        <v>28.32046230008744</v>
+        <v>110.207682779075</v>
       </c>
       <c r="D216">
-        <v>0.1810128088045772</v>
+        <v>-0.5974973502752992</v>
       </c>
       <c r="E216">
-        <v>0.8563770024540466</v>
+        <v>0.5502472186507776</v>
       </c>
     </row>
     <row r="217">
@@ -4473,16 +4473,16 @@
         </is>
       </c>
       <c r="B217">
-        <v>2.007050266977621</v>
+        <v>-111.9904556480634</v>
       </c>
       <c r="C217">
-        <v>28.32046230008713</v>
+        <v>110.2076827790738</v>
       </c>
       <c r="D217">
-        <v>0.07086926215083171</v>
+        <v>-1.016176484470356</v>
       </c>
       <c r="E217">
-        <v>0.943509332741999</v>
+        <v>0.3096758991522767</v>
       </c>
     </row>
     <row r="218">
@@ -4492,16 +4492,16 @@
         </is>
       </c>
       <c r="B218">
-        <v>38.68372697849334</v>
+        <v>94.56236518853677</v>
       </c>
       <c r="C218">
-        <v>28.32046230008711</v>
+        <v>110.2076827790737</v>
       </c>
       <c r="D218">
-        <v>1.365928513757855</v>
+        <v>0.8580378681774834</v>
       </c>
       <c r="E218">
-        <v>0.1721245174902891</v>
+        <v>0.3909807533285684</v>
       </c>
     </row>
     <row r="219">
@@ -4511,16 +4511,16 @@
         </is>
       </c>
       <c r="B219">
-        <v>-12.11704771383883</v>
+        <v>-138.0246570680452</v>
       </c>
       <c r="C219">
-        <v>28.32046230008698</v>
+        <v>110.2076827790732</v>
       </c>
       <c r="D219">
-        <v>-0.4278548699327419</v>
+        <v>-1.252405037357831</v>
       </c>
       <c r="E219">
-        <v>0.6688057128286664</v>
+        <v>0.2105778352365991</v>
       </c>
     </row>
     <row r="220">
@@ -4530,16 +4530,16 @@
         </is>
       </c>
       <c r="B220">
-        <v>-49.07397380218953</v>
+        <v>-347.0249344863544</v>
       </c>
       <c r="C220">
-        <v>28.42524124579283</v>
+        <v>110.6154248804527</v>
       </c>
       <c r="D220">
-        <v>-1.72642242075792</v>
+        <v>-3.137220101639537</v>
       </c>
       <c r="E220">
-        <v>0.08443546691935613</v>
+        <v>0.00173196666678626</v>
       </c>
     </row>
     <row r="221">
@@ -4549,16 +4549,16 @@
         </is>
       </c>
       <c r="B221">
-        <v>75.61199339635806</v>
+        <v>302.0339820231558</v>
       </c>
       <c r="C221">
-        <v>28.32046230008715</v>
+        <v>110.2076827790739</v>
       </c>
       <c r="D221">
-        <v>2.669871437661008</v>
+        <v>2.740589171343195</v>
       </c>
       <c r="E221">
-        <v>0.007653261372738585</v>
+        <v>0.006190834186633643</v>
       </c>
     </row>
     <row r="222">
@@ -4568,16 +4568,16 @@
         </is>
       </c>
       <c r="B222">
-        <v>-38.77557983900309</v>
+        <v>-290.1605715097828</v>
       </c>
       <c r="C222">
-        <v>28.32046230008704</v>
+        <v>110.2076827790735</v>
       </c>
       <c r="D222">
-        <v>-1.369171852780239</v>
+        <v>-2.632852485352131</v>
       </c>
       <c r="E222">
-        <v>0.1711088453705979</v>
+        <v>0.008536349356609775</v>
       </c>
     </row>
     <row r="223">
@@ -4587,16 +4587,16 @@
         </is>
       </c>
       <c r="B223">
-        <v>85.24675354179833</v>
+        <v>231.3664293557305</v>
       </c>
       <c r="C223">
-        <v>30.28906152519605</v>
+        <v>117.8683896072694</v>
       </c>
       <c r="D223">
-        <v>2.814440238463168</v>
+        <v>1.962921781884269</v>
       </c>
       <c r="E223">
-        <v>0.004937028632634993</v>
+        <v>0.04980227665040368</v>
       </c>
     </row>
     <row r="224">
@@ -4606,16 +4606,16 @@
         </is>
       </c>
       <c r="B224">
-        <v>17.30302602751</v>
+        <v>17.87377424805538</v>
       </c>
       <c r="C224">
-        <v>28.32046230008727</v>
+        <v>110.2076827790743</v>
       </c>
       <c r="D224">
-        <v>0.6109725838570326</v>
+        <v>0.1621826518563655</v>
       </c>
       <c r="E224">
-        <v>0.5412914726203222</v>
+        <v>0.871179421528683</v>
       </c>
     </row>
     <row r="225">
@@ -4625,16 +4625,16 @@
         </is>
       </c>
       <c r="B225">
-        <v>-38.18096959335675</v>
+        <v>-284.7058781761083</v>
       </c>
       <c r="C225">
-        <v>28.32702233870694</v>
+        <v>110.2332108459383</v>
       </c>
       <c r="D225">
-        <v>-1.34786385723236</v>
+        <v>-2.58275955123917</v>
       </c>
       <c r="E225">
-        <v>0.1778643048808022</v>
+        <v>0.009876196845831237</v>
       </c>
     </row>
     <row r="226">
@@ -4644,16 +4644,16 @@
         </is>
       </c>
       <c r="B226">
-        <v>-42.14607270158817</v>
+        <v>-285.3949406600756</v>
       </c>
       <c r="C226">
-        <v>28.32702233870699</v>
+        <v>110.2332108459385</v>
       </c>
       <c r="D226">
-        <v>-1.487839851208024</v>
+        <v>-2.589010503004784</v>
       </c>
       <c r="E226">
-        <v>0.1369605688491658</v>
+        <v>0.009699343042687559</v>
       </c>
     </row>
     <row r="227">
@@ -4663,16 +4663,16 @@
         </is>
       </c>
       <c r="B227">
-        <v>-43.95189606854416</v>
+        <v>-301.8112221539312</v>
       </c>
       <c r="C227">
-        <v>28.3204623000872</v>
+        <v>110.2076827790741</v>
       </c>
       <c r="D227">
-        <v>-1.551948396986755</v>
+        <v>-2.73856789783841</v>
       </c>
       <c r="E227">
-        <v>0.1208426175217504</v>
+        <v>0.006228864541881639</v>
       </c>
     </row>
     <row r="228">
@@ -4682,16 +4682,16 @@
         </is>
       </c>
       <c r="B228">
-        <v>-42.66170758555432</v>
+        <v>-300.730909834843</v>
       </c>
       <c r="C228">
-        <v>28.32702233870689</v>
+        <v>110.2332108459381</v>
       </c>
       <c r="D228">
-        <v>-1.506042784004872</v>
+        <v>-2.728133450228029</v>
       </c>
       <c r="E228">
-        <v>0.1322239168484471</v>
+        <v>0.006428557586582191</v>
       </c>
     </row>
     <row r="229">
@@ -4701,16 +4701,16 @@
         </is>
       </c>
       <c r="B229">
-        <v>-40.1416781177584</v>
+        <v>-298.4136840129266</v>
       </c>
       <c r="C229">
-        <v>28.32046230008732</v>
+        <v>110.2076827790746</v>
       </c>
       <c r="D229">
-        <v>-1.417408998921413</v>
+        <v>-2.707739392462639</v>
       </c>
       <c r="E229">
-        <v>0.1565288232127307</v>
+        <v>0.006835578305884536</v>
       </c>
     </row>
     <row r="230">
@@ -4720,16 +4720,16 @@
         </is>
       </c>
       <c r="B230">
-        <v>-9.663802577961743</v>
+        <v>-181.6015175446615</v>
       </c>
       <c r="C230">
-        <v>28.32046230008722</v>
+        <v>110.2076827790742</v>
       </c>
       <c r="D230">
-        <v>-0.3412303964378428</v>
+        <v>-1.647811776504781</v>
       </c>
       <c r="E230">
-        <v>0.7329682131548602</v>
+        <v>0.09955813848991941</v>
       </c>
     </row>
     <row r="231">
@@ -4739,16 +4739,16 @@
         </is>
       </c>
       <c r="B231">
-        <v>-26.62221480266535</v>
+        <v>-307.308562454463</v>
       </c>
       <c r="C231">
-        <v>28.42524124579295</v>
+        <v>110.6154248804532</v>
       </c>
       <c r="D231">
-        <v>-0.9365695289078874</v>
+        <v>-2.778170971965117</v>
       </c>
       <c r="E231">
-        <v>0.3491001321421731</v>
+        <v>0.00552081427545285</v>
       </c>
     </row>
     <row r="232">
@@ -4758,16 +4758,16 @@
         </is>
       </c>
       <c r="B232">
-        <v>-50.70497692000331</v>
+        <v>-337.7215040144555</v>
       </c>
       <c r="C232">
-        <v>28.42524124579294</v>
+        <v>110.6154248804531</v>
       </c>
       <c r="D232">
-        <v>-1.783801111186976</v>
+        <v>-3.053114015332361</v>
       </c>
       <c r="E232">
-        <v>0.07461698658082445</v>
+        <v>0.002296496081784796</v>
       </c>
     </row>
     <row r="233">
@@ -4777,16 +4777,16 @@
         </is>
       </c>
       <c r="B233">
-        <v>-47.53935569011848</v>
+        <v>-326.5060160207245</v>
       </c>
       <c r="C233">
-        <v>28.42524124579298</v>
+        <v>110.6154248804533</v>
       </c>
       <c r="D233">
-        <v>-1.672434554874867</v>
+        <v>-2.95172229708102</v>
       </c>
       <c r="E233">
-        <v>0.09460478961322516</v>
+        <v>0.003199145119766114</v>
       </c>
     </row>
     <row r="234">
@@ -4796,16 +4796,16 @@
         </is>
       </c>
       <c r="B234">
-        <v>-42.21153996213746</v>
+        <v>-317.1580256740986</v>
       </c>
       <c r="C234">
-        <v>28.32046230008728</v>
+        <v>110.2076827790744</v>
       </c>
       <c r="D234">
-        <v>-1.490496147797961</v>
+        <v>-2.877821379384984</v>
       </c>
       <c r="E234">
-        <v>0.136261312331338</v>
+        <v>0.004049458388801125</v>
       </c>
     </row>
     <row r="235">
@@ -4815,16 +4815,16 @@
         </is>
       </c>
       <c r="B235">
-        <v>-39.02086552558973</v>
+        <v>-274.3795159305164</v>
       </c>
       <c r="C235">
-        <v>28.32046230008726</v>
+        <v>110.2076827790743</v>
       </c>
       <c r="D235">
-        <v>-1.377832929142174</v>
+        <v>-2.489658697212117</v>
       </c>
       <c r="E235">
-        <v>0.1684185936642984</v>
+        <v>0.0128722834336582</v>
       </c>
     </row>
     <row r="236">
@@ -4834,16 +4834,16 @@
         </is>
       </c>
       <c r="B236">
-        <v>-22.43363812281549</v>
+        <v>-268.223659548737</v>
       </c>
       <c r="C236">
-        <v>28.32702233870679</v>
+        <v>110.2332108459377</v>
       </c>
       <c r="D236">
-        <v>-0.791951863297738</v>
+        <v>-2.433238200088422</v>
       </c>
       <c r="E236">
-        <v>0.4284884975287875</v>
+        <v>0.01505696225275987</v>
       </c>
     </row>
     <row r="237">
@@ -4853,16 +4853,16 @@
         </is>
       </c>
       <c r="B237">
-        <v>-24.59182942550835</v>
+        <v>-245.6407064743847</v>
       </c>
       <c r="C237">
-        <v>28.32702233870681</v>
+        <v>110.2332108459378</v>
       </c>
       <c r="D237">
-        <v>-0.8681402913254813</v>
+        <v>-2.228372961191276</v>
       </c>
       <c r="E237">
-        <v>0.3854281625733432</v>
+        <v>0.02597332499310968</v>
       </c>
     </row>
     <row r="238">
@@ -4872,16 +4872,16 @@
         </is>
       </c>
       <c r="B238">
-        <v>-38.25140260358731</v>
+        <v>-295.3552230056824</v>
       </c>
       <c r="C238">
-        <v>28.32046230008727</v>
+        <v>110.2076827790744</v>
       </c>
       <c r="D238">
-        <v>-1.350663071748989</v>
+        <v>-2.679987597577569</v>
       </c>
       <c r="E238">
-        <v>0.1769656753182423</v>
+        <v>0.00742664666800255</v>
       </c>
     </row>
     <row r="239">
@@ -4891,16 +4891,16 @@
         </is>
       </c>
       <c r="B239">
-        <v>-36.48126134418123</v>
+        <v>-286.1102596787896</v>
       </c>
       <c r="C239">
-        <v>28.32702233870682</v>
+        <v>110.2332108459379</v>
       </c>
       <c r="D239">
-        <v>-1.287860789177697</v>
+        <v>-2.595499645552898</v>
       </c>
       <c r="E239">
-        <v>0.1979526723134396</v>
+        <v>0.009518744216997914</v>
       </c>
     </row>
     <row r="240">
@@ -4910,16 +4910,16 @@
         </is>
       </c>
       <c r="B240">
-        <v>4.425535373133815</v>
+        <v>9.645787520577008</v>
       </c>
       <c r="C240">
-        <v>5.518835130567136</v>
+        <v>21.47627481976804</v>
       </c>
       <c r="D240">
-        <v>0.8018966445694549</v>
+        <v>0.4491369011397848</v>
       </c>
       <c r="E240">
-        <v>0.4227139315775044</v>
+        <v>0.6533845884689617</v>
       </c>
     </row>
     <row r="241">
@@ -4929,16 +4929,16 @@
         </is>
       </c>
       <c r="B241">
-        <v>-0.2638375520041212</v>
+        <v>-15.65515165473047</v>
       </c>
       <c r="C241">
-        <v>5.525512571589268</v>
+        <v>21.50225975229299</v>
       </c>
       <c r="D241">
-        <v>-0.04774897325556809</v>
+        <v>-0.7280700649642654</v>
       </c>
       <c r="E241">
-        <v>0.9619213671674942</v>
+        <v>0.4666612220328161</v>
       </c>
     </row>
     <row r="242">
@@ -4948,16 +4948,16 @@
         </is>
       </c>
       <c r="B242">
-        <v>1.335558474155324</v>
+        <v>0.4722860371658765</v>
       </c>
       <c r="C242">
-        <v>5.525512571589255</v>
+        <v>21.50225975229294</v>
       </c>
       <c r="D242">
-        <v>0.2417076165969503</v>
+        <v>0.02196448385456386</v>
       </c>
       <c r="E242">
-        <v>0.8090330459438059</v>
+        <v>0.9824786136388524</v>
       </c>
     </row>
     <row r="243">
@@ -4967,16 +4967,16 @@
         </is>
       </c>
       <c r="B243">
-        <v>8.32381452925358</v>
+        <v>41.30900866577917</v>
       </c>
       <c r="C243">
-        <v>5.518835130567138</v>
+        <v>21.47627481976804</v>
       </c>
       <c r="D243">
-        <v>1.508255697502272</v>
+        <v>1.923471785141988</v>
       </c>
       <c r="E243">
-        <v>0.1316568520015933</v>
+        <v>0.05457144264375682</v>
       </c>
     </row>
     <row r="244">
@@ -4986,16 +4986,16 @@
         </is>
       </c>
       <c r="B244">
-        <v>15.00771985103641</v>
+        <v>28.05662544499448</v>
       </c>
       <c r="C244">
-        <v>5.966927618737971</v>
+        <v>23.22000464552958</v>
       </c>
       <c r="D244">
-        <v>2.51515031017095</v>
+        <v>1.20829542772706</v>
       </c>
       <c r="E244">
-        <v>0.01198083915485964</v>
+        <v>0.2270853662224986</v>
       </c>
     </row>
     <row r="245">
@@ -5005,16 +5005,16 @@
         </is>
       </c>
       <c r="B245">
-        <v>21.24387725133703</v>
+        <v>44.40995039616486</v>
       </c>
       <c r="C245">
-        <v>6.943223265215338</v>
+        <v>27.0192110202517</v>
       </c>
       <c r="D245">
-        <v>3.059656364179752</v>
+        <v>1.643643493619347</v>
       </c>
       <c r="E245">
-        <v>0.002247169154593635</v>
+        <v>0.1004168054731314</v>
       </c>
     </row>
     <row r="246">
@@ -5024,16 +5024,16 @@
         </is>
       </c>
       <c r="B246">
-        <v>19.3048471941338</v>
+        <v>46.88555206545229</v>
       </c>
       <c r="C246">
-        <v>6.943223265215335</v>
+        <v>27.01921102025169</v>
       </c>
       <c r="D246">
-        <v>2.78038692646521</v>
+        <v>1.735267252263962</v>
       </c>
       <c r="E246">
-        <v>0.005483432876273318</v>
+        <v>0.0828570866300605</v>
       </c>
     </row>
     <row r="247">
@@ -5043,16 +5043,16 @@
         </is>
       </c>
       <c r="B247">
-        <v>16.71318947707799</v>
+        <v>24.49679590959362</v>
       </c>
       <c r="C247">
-        <v>6.968572957331253</v>
+        <v>27.11785809732464</v>
       </c>
       <c r="D247">
-        <v>2.398366147475712</v>
+        <v>0.9033455305236807</v>
       </c>
       <c r="E247">
-        <v>0.01656516833050707</v>
+        <v>0.3664580849341378</v>
       </c>
     </row>
   </sheetData>
